--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_retail_general.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_retail_general.xlsx
@@ -1397,7 +1397,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1534,22 +1534,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2413035611222518</v>
+        <v>0.2407586325755584</v>
       </c>
       <c r="C2">
-        <v>265.5432060935562</v>
+        <v>263.8762882930892</v>
       </c>
       <c r="D2">
-        <v>258.4332060935562</v>
+        <v>259.1555523141541</v>
       </c>
       <c r="E2">
-        <v>-135.3264021064878</v>
+        <v>-132.937138085423</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.389264021064879</v>
       </c>
       <c r="G2">
         <v>7.11</v>
@@ -1570,28 +1570,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1201799802595634</v>
       </c>
       <c r="N2">
-        <v>29.37466666666667</v>
+        <v>29.2544866864071</v>
       </c>
       <c r="O2">
-        <v>7.049919999999999</v>
+        <v>7.021076804737704</v>
       </c>
       <c r="P2">
-        <v>22.32474666666667</v>
+        <v>22.2334098816694</v>
       </c>
       <c r="Q2">
-        <v>25.12474666666667</v>
+        <v>25.0334098816694</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2413035611222518</v>
+        <v>0.2428043965409681</v>
       </c>
       <c r="T2">
-        <v>0.9605817593200959</v>
+        <v>0.9679559223209371</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>244.4222956537652</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1616,22 +1616,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2407586325755584</v>
+        <v>0.240213704028865</v>
       </c>
       <c r="C3">
-        <v>263.8762882930892</v>
+        <v>262.2134198684433</v>
       </c>
       <c r="D3">
-        <v>259.1555523141541</v>
+        <v>259.8819479105731</v>
       </c>
       <c r="E3">
-        <v>-132.937138085423</v>
+        <v>-130.5478740643581</v>
       </c>
       <c r="F3">
-        <v>2.389264021064879</v>
+        <v>4.778528042129757</v>
       </c>
       <c r="G3">
         <v>7.11</v>
@@ -1652,28 +1652,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M3">
-        <v>0.1201799802595634</v>
+        <v>0.2403599605191268</v>
       </c>
       <c r="N3">
-        <v>29.2544866864071</v>
+        <v>29.13430670614754</v>
       </c>
       <c r="O3">
-        <v>7.021076804737704</v>
+        <v>6.992233609475409</v>
       </c>
       <c r="P3">
-        <v>22.2334098816694</v>
+        <v>22.14207309667213</v>
       </c>
       <c r="Q3">
-        <v>25.0334098816694</v>
+        <v>24.94207309667213</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2428043965409681</v>
+        <v>0.2443358612539439</v>
       </c>
       <c r="T3">
-        <v>0.9679559223209371</v>
+        <v>0.9754805784442443</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>244.4222956537652</v>
+        <v>122.2111478268826</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1698,22 +1698,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.240213704028865</v>
+        <v>0.2396687754821716</v>
       </c>
       <c r="C4">
-        <v>262.2134198684433</v>
+        <v>260.5546349657127</v>
       </c>
       <c r="D4">
-        <v>259.8819479105731</v>
+        <v>260.6124270289073</v>
       </c>
       <c r="E4">
-        <v>-130.5478740643581</v>
+        <v>-128.1586100432932</v>
       </c>
       <c r="F4">
-        <v>4.778528042129757</v>
+        <v>7.167792063194635</v>
       </c>
       <c r="G4">
         <v>7.11</v>
@@ -1734,28 +1734,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M4">
-        <v>0.2403599605191268</v>
+        <v>0.3605399407786901</v>
       </c>
       <c r="N4">
-        <v>29.13430670614754</v>
+        <v>29.01412672588798</v>
       </c>
       <c r="O4">
-        <v>6.992233609475409</v>
+        <v>6.963390414213114</v>
       </c>
       <c r="P4">
-        <v>22.14207309667213</v>
+        <v>22.05073631167486</v>
       </c>
       <c r="Q4">
-        <v>24.94207309667213</v>
+        <v>24.85073631167486</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2443358612539439</v>
+        <v>0.2458989025589398</v>
       </c>
       <c r="T4">
-        <v>0.9754805784442443</v>
+        <v>0.9831603821164859</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>122.2111478268826</v>
+        <v>81.47409855125507</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1780,22 +1780,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2396687754821716</v>
+        <v>0.2391238469354782</v>
       </c>
       <c r="C5">
-        <v>260.5546349657127</v>
+        <v>258.8999681159865</v>
       </c>
       <c r="D5">
-        <v>260.6124270289073</v>
+        <v>261.347024200246</v>
       </c>
       <c r="E5">
-        <v>-128.1586100432932</v>
+        <v>-125.7693460222283</v>
       </c>
       <c r="F5">
-        <v>7.167792063194635</v>
+        <v>9.557056084259514</v>
       </c>
       <c r="G5">
         <v>7.11</v>
@@ -1816,28 +1816,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M5">
-        <v>0.3605399407786901</v>
+        <v>0.4807199210382536</v>
       </c>
       <c r="N5">
-        <v>29.01412672588798</v>
+        <v>28.89394674562841</v>
       </c>
       <c r="O5">
-        <v>6.963390414213114</v>
+        <v>6.934547218950819</v>
       </c>
       <c r="P5">
-        <v>22.05073631167486</v>
+        <v>21.95939952667759</v>
       </c>
       <c r="Q5">
-        <v>24.85073631167486</v>
+        <v>24.75939952667759</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2458989025589398</v>
+        <v>0.2474945072244565</v>
       </c>
       <c r="T5">
-        <v>0.9831603821164859</v>
+        <v>0.9910001816985657</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>81.47409855125507</v>
+        <v>61.1055739134413</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1862,22 +1862,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2391238469354782</v>
+        <v>0.2385789183887848</v>
       </c>
       <c r="C6">
-        <v>258.8999681159865</v>
+        <v>257.2494542407901</v>
       </c>
       <c r="D6">
-        <v>261.347024200246</v>
+        <v>262.0857743461145</v>
       </c>
       <c r="E6">
-        <v>-125.7693460222283</v>
+        <v>-123.3800820011635</v>
       </c>
       <c r="F6">
-        <v>9.557056084259514</v>
+        <v>11.94632010532439</v>
       </c>
       <c r="G6">
         <v>7.11</v>
@@ -1898,28 +1898,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M6">
-        <v>0.4807199210382536</v>
+        <v>0.6008999012978169</v>
       </c>
       <c r="N6">
-        <v>28.89394674562841</v>
+        <v>28.77376676536885</v>
       </c>
       <c r="O6">
-        <v>6.934547218950819</v>
+        <v>6.905704023688523</v>
       </c>
       <c r="P6">
-        <v>21.95939952667759</v>
+        <v>21.86806274168033</v>
       </c>
       <c r="Q6">
-        <v>24.75939952667759</v>
+        <v>24.66806274168033</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2474945072244565</v>
+        <v>0.2491237035671419</v>
       </c>
       <c r="T6">
-        <v>0.9910001816985657</v>
+        <v>0.9990050296928998</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>61.1055739134413</v>
+        <v>48.88445913075304</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1944,22 +1944,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2385789183887848</v>
+        <v>0.2380339898420914</v>
       </c>
       <c r="C7">
-        <v>257.2494542407901</v>
+        <v>255.6031286576194</v>
       </c>
       <c r="D7">
-        <v>262.0857743461145</v>
+        <v>262.8287127840086</v>
       </c>
       <c r="E7">
-        <v>-123.3800820011635</v>
+        <v>-120.9908179800986</v>
       </c>
       <c r="F7">
-        <v>11.94632010532439</v>
+        <v>14.33558412638927</v>
       </c>
       <c r="G7">
         <v>7.11</v>
@@ -1980,28 +1980,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M7">
-        <v>0.6008999012978169</v>
+        <v>0.7210798815573803</v>
       </c>
       <c r="N7">
-        <v>28.77376676536885</v>
+        <v>28.65358678510929</v>
       </c>
       <c r="O7">
-        <v>6.905704023688523</v>
+        <v>6.876860828426229</v>
       </c>
       <c r="P7">
-        <v>21.86806274168033</v>
+        <v>21.77672595668306</v>
       </c>
       <c r="Q7">
-        <v>24.66806274168033</v>
+        <v>24.57672595668306</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2491237035671419</v>
+        <v>0.2507875636617994</v>
       </c>
       <c r="T7">
-        <v>0.9990050296928998</v>
+        <v>1.007180193602007</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>48.88445913075304</v>
+        <v>40.73704927562753</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2026,22 +2026,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.2380339898420914</v>
+        <v>0.237489061295398</v>
       </c>
       <c r="C8">
-        <v>255.6031286576194</v>
+        <v>253.9610270855686</v>
       </c>
       <c r="D8">
-        <v>262.8287127840086</v>
+        <v>263.5758752330228</v>
       </c>
       <c r="E8">
-        <v>-120.9908179800986</v>
+        <v>-118.6015539590337</v>
       </c>
       <c r="F8">
-        <v>14.33558412638927</v>
+        <v>16.72484814745415</v>
       </c>
       <c r="G8">
         <v>7.11</v>
@@ -2062,28 +2062,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M8">
-        <v>0.7210798815573802</v>
+        <v>0.8412598618169436</v>
       </c>
       <c r="N8">
-        <v>28.65358678510929</v>
+        <v>28.53340680484972</v>
       </c>
       <c r="O8">
-        <v>6.876860828426229</v>
+        <v>6.848017633163933</v>
       </c>
       <c r="P8">
-        <v>21.77672595668306</v>
+        <v>21.68538917168579</v>
       </c>
       <c r="Q8">
-        <v>24.57672595668306</v>
+        <v>24.48538917168579</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2507875636617994</v>
+        <v>0.2524872056939763</v>
       </c>
       <c r="T8">
-        <v>1.007180193602007</v>
+        <v>1.015531167487654</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>40.73704927562754</v>
+        <v>34.91747080768074</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2108,22 +2108,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.237489061295398</v>
+        <v>0.2369441327487045</v>
       </c>
       <c r="C9">
-        <v>253.9610270855687</v>
+        <v>252.3231856510553</v>
       </c>
       <c r="D9">
-        <v>263.5758752330228</v>
+        <v>264.3272978195743</v>
       </c>
       <c r="E9">
-        <v>-118.6015539590337</v>
+        <v>-116.2122899379688</v>
       </c>
       <c r="F9">
-        <v>16.72484814745415</v>
+        <v>19.11411216851903</v>
       </c>
       <c r="G9">
         <v>7.11</v>
@@ -2144,28 +2144,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M9">
-        <v>0.8412598618169437</v>
+        <v>0.9614398420765071</v>
       </c>
       <c r="N9">
-        <v>28.53340680484972</v>
+        <v>28.41322682459016</v>
       </c>
       <c r="O9">
-        <v>6.848017633163933</v>
+        <v>6.819174437901638</v>
       </c>
       <c r="P9">
-        <v>21.68538917168579</v>
+        <v>21.59405238668852</v>
       </c>
       <c r="Q9">
-        <v>24.48538917168579</v>
+        <v>24.39405238668852</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2524872056939763</v>
+        <v>0.2542237964659832</v>
       </c>
       <c r="T9">
-        <v>1.015531167487654</v>
+        <v>1.024063684283859</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>34.91747080768074</v>
+        <v>30.55278695672065</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2190,22 +2190,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2369441327487045</v>
+        <v>0.2363992042020112</v>
       </c>
       <c r="C10">
-        <v>252.3231856510553</v>
+        <v>250.6896408936424</v>
       </c>
       <c r="D10">
-        <v>264.3272978195743</v>
+        <v>265.0830170832263</v>
       </c>
       <c r="E10">
-        <v>-116.2122899379688</v>
+        <v>-113.8230259169039</v>
       </c>
       <c r="F10">
-        <v>19.11411216851903</v>
+        <v>21.5033761895839</v>
       </c>
       <c r="G10">
         <v>7.11</v>
@@ -2226,28 +2226,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M10">
-        <v>0.9614398420765071</v>
+        <v>1.08161982233607</v>
       </c>
       <c r="N10">
-        <v>28.41322682459016</v>
+        <v>28.2930468443306</v>
       </c>
       <c r="O10">
-        <v>6.819174437901638</v>
+        <v>6.790331242639343</v>
       </c>
       <c r="P10">
-        <v>21.59405238668852</v>
+        <v>21.50271560169125</v>
       </c>
       <c r="Q10">
-        <v>24.39405238668852</v>
+        <v>24.30271560169125</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2542237964659832</v>
+        <v>0.2559985540681441</v>
       </c>
       <c r="T10">
-        <v>1.024063684283859</v>
+        <v>1.032783728921738</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>30.55278695672065</v>
+        <v>27.15803285041836</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2272,22 +2272,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.2363992042020112</v>
+        <v>0.2358542756553178</v>
       </c>
       <c r="C11">
-        <v>250.6896408936424</v>
+        <v>249.0604297719622</v>
       </c>
       <c r="D11">
-        <v>265.0830170832263</v>
+        <v>265.8430699826109</v>
       </c>
       <c r="E11">
-        <v>-113.8230259169039</v>
+        <v>-111.4337618958391</v>
       </c>
       <c r="F11">
-        <v>21.5033761895839</v>
+        <v>23.89264021064878</v>
       </c>
       <c r="G11">
         <v>7.11</v>
@@ -2308,28 +2308,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M11">
-        <v>1.08161982233607</v>
+        <v>1.201799802595634</v>
       </c>
       <c r="N11">
-        <v>28.2930468443306</v>
+        <v>28.17286686407103</v>
       </c>
       <c r="O11">
-        <v>6.790331242639343</v>
+        <v>6.761488047377047</v>
       </c>
       <c r="P11">
-        <v>21.50271560169125</v>
+        <v>21.41137881669399</v>
       </c>
       <c r="Q11">
-        <v>24.30271560169125</v>
+        <v>24.21137881669399</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2559985540681441</v>
+        <v>0.2578127507281309</v>
       </c>
       <c r="T11">
-        <v>1.032783728921738</v>
+        <v>1.041697552329349</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>27.15803285041836</v>
+        <v>24.44222956537653</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2354,22 +2354,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.2358542756553178</v>
+        <v>0.2353093471086244</v>
       </c>
       <c r="C12">
-        <v>249.0604297719622</v>
+        <v>247.4355896697402</v>
       </c>
       <c r="D12">
-        <v>265.8430699826109</v>
+        <v>266.6074939014538</v>
       </c>
       <c r="E12">
-        <v>-111.4337618958391</v>
+        <v>-109.0444978747742</v>
       </c>
       <c r="F12">
-        <v>23.89264021064879</v>
+        <v>26.28190423171366</v>
       </c>
       <c r="G12">
         <v>7.11</v>
@@ -2390,28 +2390,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M12">
-        <v>1.201799802595634</v>
+        <v>1.321979782855197</v>
       </c>
       <c r="N12">
-        <v>28.17286686407103</v>
+        <v>28.05268688381147</v>
       </c>
       <c r="O12">
-        <v>6.761488047377047</v>
+        <v>6.732644852114752</v>
       </c>
       <c r="P12">
-        <v>21.41137881669399</v>
+        <v>21.32004203169672</v>
       </c>
       <c r="Q12">
-        <v>24.21137881669399</v>
+        <v>24.12004203169672</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2578127507281309</v>
+        <v>0.259667715852387</v>
       </c>
       <c r="T12">
-        <v>1.041697552329349</v>
+        <v>1.050811686375332</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>24.44222956537652</v>
+        <v>22.22020869579683</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2436,22 +2436,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.2353093471086244</v>
+        <v>0.234764418561931</v>
       </c>
       <c r="C13">
-        <v>247.4355896697402</v>
+        <v>245.8151584019255</v>
       </c>
       <c r="D13">
-        <v>266.6074939014538</v>
+        <v>267.376326654704</v>
       </c>
       <c r="E13">
-        <v>-109.0444978747742</v>
+        <v>-106.6552338537093</v>
       </c>
       <c r="F13">
-        <v>26.28190423171366</v>
+        <v>28.67116825277854</v>
       </c>
       <c r="G13">
         <v>7.11</v>
@@ -2472,28 +2472,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M13">
-        <v>1.321979782855197</v>
+        <v>1.44215976311476</v>
       </c>
       <c r="N13">
-        <v>28.05268688381147</v>
+        <v>27.93250690355191</v>
       </c>
       <c r="O13">
-        <v>6.732644852114752</v>
+        <v>6.703801656852457</v>
       </c>
       <c r="P13">
-        <v>21.32004203169672</v>
+        <v>21.22870524669945</v>
       </c>
       <c r="Q13">
-        <v>24.12004203169672</v>
+        <v>24.02870524669945</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.259667715852387</v>
+        <v>0.2615648392749216</v>
       </c>
       <c r="T13">
-        <v>1.050811686375332</v>
+        <v>1.060132959831451</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>22.22020869579683</v>
+        <v>20.36852463781377</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2518,22 +2518,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.234764418561931</v>
+        <v>0.2342194900152376</v>
       </c>
       <c r="C14">
-        <v>245.8151584019255</v>
+        <v>244.199174220926</v>
       </c>
       <c r="D14">
-        <v>267.376326654704</v>
+        <v>268.1496064947694</v>
       </c>
       <c r="E14">
-        <v>-106.6552338537093</v>
+        <v>-104.2659698326444</v>
       </c>
       <c r="F14">
-        <v>28.67116825277854</v>
+        <v>31.06043227384342</v>
       </c>
       <c r="G14">
         <v>7.11</v>
@@ -2554,28 +2554,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M14">
-        <v>1.44215976311476</v>
+        <v>1.562339743374324</v>
       </c>
       <c r="N14">
-        <v>27.93250690355191</v>
+        <v>27.81232692329234</v>
       </c>
       <c r="O14">
-        <v>6.703801656852457</v>
+        <v>6.674958461590162</v>
       </c>
       <c r="P14">
-        <v>21.22870524669945</v>
+        <v>21.13736846170218</v>
       </c>
       <c r="Q14">
-        <v>24.02870524669945</v>
+        <v>23.93736846170218</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2615648392749216</v>
+        <v>0.2635055747301581</v>
       </c>
       <c r="T14">
-        <v>1.060132959831451</v>
+        <v>1.069668515435987</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>20.36852463781377</v>
+        <v>18.80171505028963</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2600,22 +2600,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.2342194900152376</v>
+        <v>0.2336745614685442</v>
       </c>
       <c r="C15">
-        <v>244.199174220926</v>
+        <v>242.5876758229524</v>
       </c>
       <c r="D15">
-        <v>268.1496064947694</v>
+        <v>268.9273721178607</v>
       </c>
       <c r="E15">
-        <v>-104.2659698326444</v>
+        <v>-101.8767058115795</v>
       </c>
       <c r="F15">
-        <v>31.06043227384342</v>
+        <v>33.4496962949083</v>
       </c>
       <c r="G15">
         <v>7.11</v>
@@ -2636,28 +2636,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M15">
-        <v>1.562339743374324</v>
+        <v>1.682519723633887</v>
       </c>
       <c r="N15">
-        <v>27.81232692329234</v>
+        <v>27.69214694303278</v>
       </c>
       <c r="O15">
-        <v>6.674958461590162</v>
+        <v>6.646115266327866</v>
       </c>
       <c r="P15">
-        <v>21.13736846170218</v>
+        <v>21.04603167670491</v>
       </c>
       <c r="Q15">
-        <v>23.93736846170218</v>
+        <v>23.84603167670491</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2635055747301581</v>
+        <v>0.2654914435680746</v>
       </c>
       <c r="T15">
-        <v>1.069668515435987</v>
+        <v>1.079425828147605</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>18.80171505028963</v>
+        <v>17.45873540384037</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2682,22 +2682,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.2336745614685442</v>
+        <v>0.2331296329218508</v>
       </c>
       <c r="C16">
-        <v>242.5876758229524</v>
+        <v>240.980702354474</v>
       </c>
       <c r="D16">
-        <v>268.9273721178607</v>
+        <v>269.7096626704471</v>
       </c>
       <c r="E16">
-        <v>-101.8767058115795</v>
+        <v>-99.48744179051467</v>
       </c>
       <c r="F16">
-        <v>33.4496962949083</v>
+        <v>35.83896031597318</v>
       </c>
       <c r="G16">
         <v>7.11</v>
@@ -2718,28 +2718,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M16">
-        <v>1.682519723633887</v>
+        <v>1.802699703893451</v>
       </c>
       <c r="N16">
-        <v>27.69214694303278</v>
+        <v>27.57196696277321</v>
       </c>
       <c r="O16">
-        <v>6.646115266327866</v>
+        <v>6.617272071065571</v>
       </c>
       <c r="P16">
-        <v>21.04603167670491</v>
+        <v>20.95469489170764</v>
       </c>
       <c r="Q16">
-        <v>23.84603167670491</v>
+        <v>23.75469489170764</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2654914435680746</v>
+        <v>0.2675240387315892</v>
       </c>
       <c r="T16">
-        <v>1.079425828147605</v>
+        <v>1.089412724687733</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>17.45873540384037</v>
+        <v>16.29481971025101</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2764,22 +2764,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.2331296329218508</v>
+        <v>0.2325847043751574</v>
       </c>
       <c r="C17">
-        <v>240.980702354474</v>
+        <v>239.3782934187859</v>
       </c>
       <c r="D17">
-        <v>269.7096626704472</v>
+        <v>270.4965177558239</v>
       </c>
       <c r="E17">
-        <v>-99.48744179051468</v>
+        <v>-97.09817776944979</v>
       </c>
       <c r="F17">
-        <v>35.83896031597317</v>
+        <v>38.22822433703806</v>
       </c>
       <c r="G17">
         <v>7.11</v>
@@ -2800,28 +2800,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M17">
-        <v>1.802699703893451</v>
+        <v>1.922879684153014</v>
       </c>
       <c r="N17">
-        <v>27.57196696277322</v>
+        <v>27.45178698251365</v>
       </c>
       <c r="O17">
-        <v>6.617272071065572</v>
+        <v>6.588428875803277</v>
       </c>
       <c r="P17">
-        <v>20.95469489170765</v>
+        <v>20.86335810671038</v>
       </c>
       <c r="Q17">
-        <v>23.75469489170765</v>
+        <v>23.66335810671038</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2675240387315891</v>
+        <v>0.2696050290180445</v>
       </c>
       <c r="T17">
-        <v>1.089412724687732</v>
+        <v>1.099637404478815</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.29481971025101</v>
+        <v>15.27639347836032</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2846,22 +2846,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.2325847043751574</v>
+        <v>0.2320397758284639</v>
       </c>
       <c r="C18">
-        <v>239.3782934187859</v>
+        <v>237.7804890826922</v>
       </c>
       <c r="D18">
-        <v>270.4965177558239</v>
+        <v>271.2879774407951</v>
       </c>
       <c r="E18">
-        <v>-97.09817776944979</v>
+        <v>-94.7089137483849</v>
       </c>
       <c r="F18">
-        <v>38.22822433703806</v>
+        <v>40.61748835810294</v>
       </c>
       <c r="G18">
         <v>7.11</v>
@@ -2882,28 +2882,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M18">
-        <v>1.922879684153014</v>
+        <v>2.043059664412578</v>
       </c>
       <c r="N18">
-        <v>27.45178698251365</v>
+        <v>27.33160700225409</v>
       </c>
       <c r="O18">
-        <v>6.588428875803277</v>
+        <v>6.559585680540981</v>
       </c>
       <c r="P18">
-        <v>20.86335810671038</v>
+        <v>20.77202132171311</v>
       </c>
       <c r="Q18">
-        <v>23.66335810671038</v>
+        <v>23.57202132171311</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2696050290180445</v>
+        <v>0.2717361636487517</v>
       </c>
       <c r="T18">
-        <v>1.099637404478815</v>
+        <v>1.110108462096188</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2920,7 +2920,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.27639347836032</v>
+        <v>14.3777820972803</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2928,22 +2928,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.2320397758284639</v>
+        <v>0.2314948472817706</v>
       </c>
       <c r="C19">
-        <v>237.7804890826922</v>
+        <v>236.1873298833076</v>
       </c>
       <c r="D19">
-        <v>271.2879774407951</v>
+        <v>272.0840822624754</v>
       </c>
       <c r="E19">
-        <v>-94.7089137483849</v>
+        <v>-92.31964972732004</v>
       </c>
       <c r="F19">
-        <v>40.61748835810294</v>
+        <v>43.00675237916781</v>
       </c>
       <c r="G19">
         <v>7.11</v>
@@ -2964,28 +2964,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M19">
-        <v>2.043059664412578</v>
+        <v>2.163239644672141</v>
       </c>
       <c r="N19">
-        <v>27.33160700225409</v>
+        <v>27.21142702199452</v>
       </c>
       <c r="O19">
-        <v>6.559585680540981</v>
+        <v>6.530742485278686</v>
       </c>
       <c r="P19">
-        <v>20.77202132171311</v>
+        <v>20.68068453671584</v>
       </c>
       <c r="Q19">
-        <v>23.57202132171311</v>
+        <v>23.48068453671584</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2717361636487517</v>
+        <v>0.2739192771728909</v>
       </c>
       <c r="T19">
-        <v>1.110108462096188</v>
+        <v>1.120834911362766</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.3777820972803</v>
+        <v>13.57901642520918</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3010,22 +3010,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.2314948472817706</v>
+        <v>0.2311665187350772</v>
       </c>
       <c r="C20">
-        <v>236.1873298833076</v>
+        <v>234.2799920046618</v>
       </c>
       <c r="D20">
-        <v>272.0840822624754</v>
+        <v>272.5660084048945</v>
       </c>
       <c r="E20">
-        <v>-92.31964972732004</v>
+        <v>-89.93038570625515</v>
       </c>
       <c r="F20">
-        <v>43.00675237916781</v>
+        <v>45.39601640023269</v>
       </c>
       <c r="G20">
         <v>7.11</v>
@@ -3046,45 +3046,45 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M20">
-        <v>2.16323964467214</v>
+        <v>2.351513649532053</v>
       </c>
       <c r="N20">
-        <v>27.21142702199452</v>
+        <v>27.02315301713461</v>
       </c>
       <c r="O20">
-        <v>6.530742485278686</v>
+        <v>6.485556724112307</v>
       </c>
       <c r="P20">
-        <v>20.68068453671584</v>
+        <v>20.53759629302231</v>
       </c>
       <c r="Q20">
-        <v>23.48068453671584</v>
+        <v>23.33759629302231</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2739192771728909</v>
+        <v>0.2761562947346631</v>
       </c>
       <c r="T20">
-        <v>1.120834911362766</v>
+        <v>1.131826211228518</v>
       </c>
       <c r="U20">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.24</v>
       </c>
       <c r="W20">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>13.57901642520918</v>
+        <v>12.49181210260556</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3092,22 +3092,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.2311665187350772</v>
+        <v>0.2306329901883837</v>
       </c>
       <c r="C21">
-        <v>234.2799920046618</v>
+        <v>232.6775017418642</v>
       </c>
       <c r="D21">
-        <v>272.5660084048945</v>
+        <v>273.3527821631617</v>
       </c>
       <c r="E21">
-        <v>-89.93038570625515</v>
+        <v>-87.54112168519028</v>
       </c>
       <c r="F21">
-        <v>45.39601640023269</v>
+        <v>47.78528042129757</v>
       </c>
       <c r="G21">
         <v>7.11</v>
@@ -3128,28 +3128,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M21">
-        <v>2.351513649532053</v>
+        <v>2.475277525823214</v>
       </c>
       <c r="N21">
-        <v>27.02315301713461</v>
+        <v>26.89938914084345</v>
       </c>
       <c r="O21">
-        <v>6.485556724112307</v>
+        <v>6.455853393802428</v>
       </c>
       <c r="P21">
-        <v>20.53759629302231</v>
+        <v>20.44353574704103</v>
       </c>
       <c r="Q21">
-        <v>23.33759629302231</v>
+        <v>23.24353574704103</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2761562947346631</v>
+        <v>0.2784492377354796</v>
       </c>
       <c r="T21">
-        <v>1.131826211228518</v>
+        <v>1.143092293590914</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>12.49181210260556</v>
+        <v>11.86722149747528</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3174,22 +3174,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.2306329901883837</v>
+        <v>0.2300994616416903</v>
       </c>
       <c r="C22">
-        <v>232.6775017418642</v>
+        <v>231.0795667420726</v>
       </c>
       <c r="D22">
-        <v>273.3527821631617</v>
+        <v>274.144111184435</v>
       </c>
       <c r="E22">
-        <v>-87.54112168519028</v>
+        <v>-85.1518576641254</v>
       </c>
       <c r="F22">
-        <v>47.78528042129757</v>
+        <v>50.17454444236245</v>
       </c>
       <c r="G22">
         <v>7.11</v>
@@ -3210,28 +3210,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M22">
-        <v>2.475277525823214</v>
+        <v>2.599041402114375</v>
       </c>
       <c r="N22">
-        <v>26.89938914084345</v>
+        <v>26.77562526455229</v>
       </c>
       <c r="O22">
-        <v>6.455853393802428</v>
+        <v>6.42615006349255</v>
       </c>
       <c r="P22">
-        <v>20.44353574704103</v>
+        <v>20.34947520105974</v>
       </c>
       <c r="Q22">
-        <v>23.24353574704103</v>
+        <v>23.14947520105974</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2784492377354796</v>
+        <v>0.2808002299261903</v>
       </c>
       <c r="T22">
-        <v>1.143092293590914</v>
+        <v>1.154643593228308</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.86722149747528</v>
+        <v>11.30211571188122</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3256,22 +3256,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2300994616416903</v>
+        <v>0.229565933094997</v>
       </c>
       <c r="C23">
-        <v>231.0795667420726</v>
+        <v>229.4862266812402</v>
       </c>
       <c r="D23">
-        <v>274.144111184435</v>
+        <v>274.9400351446675</v>
       </c>
       <c r="E23">
-        <v>-85.1518576641254</v>
+        <v>-82.76259364306051</v>
       </c>
       <c r="F23">
-        <v>50.17454444236245</v>
+        <v>52.56380846342733</v>
       </c>
       <c r="G23">
         <v>7.11</v>
@@ -3292,28 +3292,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M23">
-        <v>2.599041402114375</v>
+        <v>2.722805278405536</v>
       </c>
       <c r="N23">
-        <v>26.77562526455229</v>
+        <v>26.65186138826113</v>
       </c>
       <c r="O23">
-        <v>6.42615006349255</v>
+        <v>6.396446733182671</v>
       </c>
       <c r="P23">
-        <v>20.34947520105974</v>
+        <v>20.25541465507846</v>
       </c>
       <c r="Q23">
-        <v>23.14947520105974</v>
+        <v>23.05541465507846</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2808002299261903</v>
+        <v>0.2832115039679448</v>
       </c>
       <c r="T23">
-        <v>1.154643593228308</v>
+        <v>1.166491080035891</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.30211571188122</v>
+        <v>10.78838317952298</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3338,22 +3338,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.229565933094997</v>
+        <v>0.2290324045483035</v>
       </c>
       <c r="C24">
-        <v>229.4862266812402</v>
+        <v>227.8975216974274</v>
       </c>
       <c r="D24">
-        <v>274.9400351446675</v>
+        <v>275.7405941819196</v>
       </c>
       <c r="E24">
-        <v>-82.76259364306051</v>
+        <v>-80.37332962199565</v>
       </c>
       <c r="F24">
-        <v>52.56380846342733</v>
+        <v>54.9530724844922</v>
       </c>
       <c r="G24">
         <v>7.11</v>
@@ -3374,28 +3374,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M24">
-        <v>2.722805278405536</v>
+        <v>2.846569154696696</v>
       </c>
       <c r="N24">
-        <v>26.65186138826113</v>
+        <v>26.52809751196997</v>
       </c>
       <c r="O24">
-        <v>6.396446733182671</v>
+        <v>6.366743402872793</v>
       </c>
       <c r="P24">
-        <v>20.25541465507846</v>
+        <v>20.16135410909718</v>
       </c>
       <c r="Q24">
-        <v>23.05541465507846</v>
+        <v>22.96135410909718</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2832115039679448</v>
+        <v>0.2856854085042903</v>
       </c>
       <c r="T24">
-        <v>1.166491080035891</v>
+        <v>1.178646293773541</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.78838317952298</v>
+        <v>10.31932304128285</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3420,22 +3420,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2290324045483035</v>
+        <v>0.2284988760016102</v>
       </c>
       <c r="C25">
-        <v>227.8975216974274</v>
+        <v>226.313492397549</v>
       </c>
       <c r="D25">
-        <v>275.7405941819196</v>
+        <v>276.545828903106</v>
       </c>
       <c r="E25">
-        <v>-80.37332962199565</v>
+        <v>-77.98406560093076</v>
       </c>
       <c r="F25">
-        <v>54.9530724844922</v>
+        <v>57.34233650555709</v>
       </c>
       <c r="G25">
         <v>7.11</v>
@@ -3456,28 +3456,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M25">
-        <v>2.846569154696696</v>
+        <v>2.970333030987857</v>
       </c>
       <c r="N25">
-        <v>26.52809751196997</v>
+        <v>26.40433363567881</v>
       </c>
       <c r="O25">
-        <v>6.366743402872793</v>
+        <v>6.337040072562914</v>
       </c>
       <c r="P25">
-        <v>20.16135410909718</v>
+        <v>20.0672935631159</v>
       </c>
       <c r="Q25">
-        <v>22.96135410909718</v>
+        <v>22.8672935631159</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2856854085042903</v>
+        <v>0.2882244157915923</v>
       </c>
       <c r="T25">
-        <v>1.178646293773541</v>
+        <v>1.191121381556919</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.31932304128285</v>
+        <v>9.889351247896066</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3502,22 +3502,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2284988760016102</v>
+        <v>0.2282883474549167</v>
       </c>
       <c r="C26">
-        <v>226.313492397549</v>
+        <v>224.2432667823061</v>
       </c>
       <c r="D26">
-        <v>276.545828903106</v>
+        <v>276.864867308928</v>
       </c>
       <c r="E26">
-        <v>-77.98406560093076</v>
+        <v>-75.59480157986589</v>
       </c>
       <c r="F26">
-        <v>57.34233650555708</v>
+        <v>59.73160052662196</v>
       </c>
       <c r="G26">
         <v>7.11</v>
@@ -3538,45 +3538,45 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M26">
-        <v>2.970333030987856</v>
+        <v>3.195640628174275</v>
       </c>
       <c r="N26">
-        <v>26.40433363567881</v>
+        <v>26.17902603849239</v>
       </c>
       <c r="O26">
-        <v>6.337040072562914</v>
+        <v>6.282966249238174</v>
       </c>
       <c r="P26">
-        <v>20.0672935631159</v>
+        <v>19.89605978925422</v>
       </c>
       <c r="Q26">
-        <v>22.8672935631159</v>
+        <v>22.69605978925422</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2882244157915923</v>
+        <v>0.290831129939889</v>
       </c>
       <c r="T26">
-        <v>1.191121381556919</v>
+        <v>1.203929138347854</v>
       </c>
       <c r="U26">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V26">
         <v>0.24</v>
       </c>
       <c r="W26">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>9.889351247896068</v>
+        <v>9.192105772997675</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3584,22 +3584,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2282883474549167</v>
+        <v>0.2277677389082233</v>
       </c>
       <c r="C27">
-        <v>224.2432667823061</v>
+        <v>222.6461113903035</v>
       </c>
       <c r="D27">
-        <v>276.864867308928</v>
+        <v>277.6569759379904</v>
       </c>
       <c r="E27">
-        <v>-75.59480157986589</v>
+        <v>-73.20553755880101</v>
       </c>
       <c r="F27">
-        <v>59.73160052662196</v>
+        <v>62.12086454768684</v>
       </c>
       <c r="G27">
         <v>7.11</v>
@@ -3620,28 +3620,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M27">
-        <v>3.195640628174275</v>
+        <v>3.323466253301246</v>
       </c>
       <c r="N27">
-        <v>26.17902603849239</v>
+        <v>26.05120041336542</v>
       </c>
       <c r="O27">
-        <v>6.282966249238174</v>
+        <v>6.252288099207701</v>
       </c>
       <c r="P27">
-        <v>19.89605978925422</v>
+        <v>19.79891231415772</v>
       </c>
       <c r="Q27">
-        <v>22.69605978925422</v>
+        <v>22.59891231415772</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.290831129939889</v>
+        <v>0.2935082958219234</v>
       </c>
       <c r="T27">
-        <v>1.203929138347854</v>
+        <v>1.217083050727732</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.192105772997675</v>
+        <v>8.838563243266995</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3666,22 +3666,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2277677389082233</v>
+        <v>0.2272471303615299</v>
       </c>
       <c r="C28">
-        <v>222.6461113903035</v>
+        <v>221.0535014383019</v>
       </c>
       <c r="D28">
-        <v>277.6569759379904</v>
+        <v>278.4536300070536</v>
       </c>
       <c r="E28">
-        <v>-73.20553755880101</v>
+        <v>-70.81627353773612</v>
       </c>
       <c r="F28">
-        <v>62.12086454768684</v>
+        <v>64.51012856875172</v>
       </c>
       <c r="G28">
         <v>7.11</v>
@@ -3702,28 +3702,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M28">
-        <v>3.323466253301246</v>
+        <v>3.451291878428217</v>
       </c>
       <c r="N28">
-        <v>26.05120041336542</v>
+        <v>25.92337478823845</v>
       </c>
       <c r="O28">
-        <v>6.252288099207701</v>
+        <v>6.221609949177227</v>
       </c>
       <c r="P28">
-        <v>19.79891231415772</v>
+        <v>19.70176483906122</v>
       </c>
       <c r="Q28">
-        <v>22.59891231415772</v>
+        <v>22.50176483906122</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2935082958219234</v>
+        <v>0.2962588087144246</v>
       </c>
       <c r="T28">
-        <v>1.217083050727732</v>
+        <v>1.230597344268704</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.838563243266995</v>
+        <v>8.511209049071919</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3748,22 +3748,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2272471303615299</v>
+        <v>0.2267265218148365</v>
       </c>
       <c r="C29">
-        <v>221.0535014383019</v>
+        <v>219.4654761642452</v>
       </c>
       <c r="D29">
-        <v>278.4536300070536</v>
+        <v>279.2548687540618</v>
       </c>
       <c r="E29">
-        <v>-70.81627353773612</v>
+        <v>-68.42700951667125</v>
       </c>
       <c r="F29">
-        <v>64.51012856875172</v>
+        <v>66.8993925898166</v>
       </c>
       <c r="G29">
         <v>7.11</v>
@@ -3784,28 +3784,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M29">
-        <v>3.451291878428217</v>
+        <v>3.579117503555188</v>
       </c>
       <c r="N29">
-        <v>25.92337478823845</v>
+        <v>25.79554916311148</v>
       </c>
       <c r="O29">
-        <v>6.221609949177227</v>
+        <v>6.190931799146754</v>
       </c>
       <c r="P29">
-        <v>19.70176483906122</v>
+        <v>19.60461736396472</v>
       </c>
       <c r="Q29">
-        <v>22.50176483906122</v>
+        <v>22.40461736396473</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2962588087144246</v>
+        <v>0.2990857247428285</v>
       </c>
       <c r="T29">
-        <v>1.230597344268704</v>
+        <v>1.24448703485248</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.511209049071919</v>
+        <v>8.207237297319352</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3830,22 +3830,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2267265218148365</v>
+        <v>0.2262059132681431</v>
       </c>
       <c r="C30">
-        <v>219.4654761642452</v>
+        <v>217.882075259003</v>
       </c>
       <c r="D30">
-        <v>279.2548687540618</v>
+        <v>280.0607318698845</v>
       </c>
       <c r="E30">
-        <v>-68.42700951667125</v>
+        <v>-66.03774549560636</v>
       </c>
       <c r="F30">
-        <v>66.8993925898166</v>
+        <v>69.28865661088149</v>
       </c>
       <c r="G30">
         <v>7.11</v>
@@ -3866,28 +3866,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M30">
-        <v>3.579117503555188</v>
+        <v>3.706943128682159</v>
       </c>
       <c r="N30">
-        <v>25.79554916311148</v>
+        <v>25.66772353798451</v>
       </c>
       <c r="O30">
-        <v>6.190931799146754</v>
+        <v>6.160253649116282</v>
       </c>
       <c r="P30">
-        <v>19.60461736396472</v>
+        <v>19.50746988886823</v>
       </c>
       <c r="Q30">
-        <v>22.40461736396473</v>
+        <v>22.30746988886823</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2990857247428285</v>
+        <v>0.3019922722086523</v>
       </c>
       <c r="T30">
-        <v>1.24448703485248</v>
+        <v>1.25876798432594</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.207237297319352</v>
+        <v>7.924229114653166</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3912,22 +3912,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2262059132681431</v>
+        <v>0.2256853047214497</v>
       </c>
       <c r="C31">
-        <v>217.8820752590031</v>
+        <v>216.3033388729245</v>
       </c>
       <c r="D31">
-        <v>280.0607318698845</v>
+        <v>280.8712595048709</v>
       </c>
       <c r="E31">
-        <v>-66.03774549560637</v>
+        <v>-63.6484814745415</v>
       </c>
       <c r="F31">
-        <v>69.28865661088147</v>
+        <v>71.67792063194635</v>
       </c>
       <c r="G31">
         <v>7.11</v>
@@ -3948,28 +3948,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M31">
-        <v>3.706943128682159</v>
+        <v>3.83476875380913</v>
       </c>
       <c r="N31">
-        <v>25.66772353798451</v>
+        <v>25.53989791285754</v>
       </c>
       <c r="O31">
-        <v>6.160253649116282</v>
+        <v>6.129575499085808</v>
       </c>
       <c r="P31">
-        <v>19.50746988886823</v>
+        <v>19.41032241377173</v>
       </c>
       <c r="Q31">
-        <v>22.30746988886823</v>
+        <v>22.21032241377173</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.3019922722086523</v>
+        <v>0.3049818638877853</v>
       </c>
       <c r="T31">
-        <v>1.25876798432594</v>
+        <v>1.273456960927213</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.924229114653167</v>
+        <v>7.660088144164729</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3994,22 +3994,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2256853047214497</v>
+        <v>0.2253531761747563</v>
       </c>
       <c r="C32">
-        <v>216.3033388729245</v>
+        <v>214.4336165565216</v>
       </c>
       <c r="D32">
-        <v>280.8712595048709</v>
+        <v>281.3908012095328</v>
       </c>
       <c r="E32">
-        <v>-63.6484814745415</v>
+        <v>-61.25921745347662</v>
       </c>
       <c r="F32">
-        <v>71.67792063194635</v>
+        <v>74.06718465301122</v>
       </c>
       <c r="G32">
         <v>7.11</v>
@@ -4030,45 +4030,45 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M32">
-        <v>3.83476875380913</v>
+        <v>4.02184812665851</v>
       </c>
       <c r="N32">
-        <v>25.53989791285754</v>
+        <v>25.35281854000816</v>
       </c>
       <c r="O32">
-        <v>6.129575499085808</v>
+        <v>6.084676449601957</v>
       </c>
       <c r="P32">
-        <v>19.41032241377173</v>
+        <v>19.2681420904062</v>
       </c>
       <c r="Q32">
-        <v>22.21032241377173</v>
+        <v>22.0681420904062</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.3049818638877853</v>
+        <v>0.3080581103981975</v>
       </c>
       <c r="T32">
-        <v>1.273456960927213</v>
+        <v>1.288571704966204</v>
       </c>
       <c r="U32">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V32">
         <v>0.24</v>
       </c>
       <c r="W32">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y32">
-        <v>7.660088144164729</v>
+        <v>7.303773226034806</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4076,22 +4076,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2253531761747563</v>
+        <v>0.2248386476280629</v>
       </c>
       <c r="C33">
-        <v>214.4336165565216</v>
+        <v>212.8530248635677</v>
       </c>
       <c r="D33">
-        <v>281.3908012095328</v>
+        <v>282.1994735376438</v>
       </c>
       <c r="E33">
-        <v>-61.25921745347662</v>
+        <v>-58.86995343241173</v>
       </c>
       <c r="F33">
-        <v>74.06718465301122</v>
+        <v>76.45644867407611</v>
       </c>
       <c r="G33">
         <v>7.11</v>
@@ -4112,28 +4112,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M33">
-        <v>4.02184812665851</v>
+        <v>4.151585163002333</v>
       </c>
       <c r="N33">
-        <v>25.35281854000816</v>
+        <v>25.22308150366433</v>
       </c>
       <c r="O33">
-        <v>6.084676449601957</v>
+        <v>6.05353956087944</v>
       </c>
       <c r="P33">
-        <v>19.2681420904062</v>
+        <v>19.16954194278489</v>
       </c>
       <c r="Q33">
-        <v>22.0681420904062</v>
+        <v>21.96954194278489</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.3080581103981975</v>
+        <v>0.3112248347471513</v>
       </c>
       <c r="T33">
-        <v>1.288571704966204</v>
+        <v>1.30413100030046</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.303773226034806</v>
+        <v>7.075530312721217</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4158,22 +4158,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2248386476280629</v>
+        <v>0.2243241190813695</v>
       </c>
       <c r="C34">
-        <v>212.8530248635677</v>
+        <v>211.2770945575444</v>
       </c>
       <c r="D34">
-        <v>282.1994735376438</v>
+        <v>283.0128072526854</v>
       </c>
       <c r="E34">
-        <v>-58.86995343241173</v>
+        <v>-56.48068941134686</v>
       </c>
       <c r="F34">
-        <v>76.45644867407611</v>
+        <v>78.84571269514099</v>
       </c>
       <c r="G34">
         <v>7.11</v>
@@ -4194,28 +4194,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M34">
-        <v>4.151585163002333</v>
+        <v>4.281322199346156</v>
       </c>
       <c r="N34">
-        <v>25.22308150366433</v>
+        <v>25.09334446732051</v>
       </c>
       <c r="O34">
-        <v>6.05353956087944</v>
+        <v>6.022402672156922</v>
       </c>
       <c r="P34">
-        <v>19.16954194278489</v>
+        <v>19.07094179516359</v>
       </c>
       <c r="Q34">
-        <v>21.96954194278489</v>
+        <v>21.87094179516359</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.3112248347471513</v>
+        <v>0.3144860881811485</v>
       </c>
       <c r="T34">
-        <v>1.30413100030046</v>
+        <v>1.320154752211857</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.075530312721217</v>
+        <v>6.861120303244817</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4240,22 +4240,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.2243241190813695</v>
+        <v>0.2238095905346761</v>
       </c>
       <c r="C35">
-        <v>211.2770945575444</v>
+        <v>209.7058660590262</v>
       </c>
       <c r="D35">
-        <v>283.0128072526854</v>
+        <v>283.830842775232</v>
       </c>
       <c r="E35">
-        <v>-56.48068941134686</v>
+        <v>-54.09142539028197</v>
       </c>
       <c r="F35">
-        <v>78.84571269514099</v>
+        <v>81.23497671620588</v>
       </c>
       <c r="G35">
         <v>7.11</v>
@@ -4276,28 +4276,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M35">
-        <v>4.281322199346156</v>
+        <v>4.411059235689979</v>
       </c>
       <c r="N35">
-        <v>25.09334446732051</v>
+        <v>24.96360743097669</v>
       </c>
       <c r="O35">
-        <v>6.022402672156922</v>
+        <v>5.991265783434405</v>
       </c>
       <c r="P35">
-        <v>19.07094179516359</v>
+        <v>18.97234164754228</v>
       </c>
       <c r="Q35">
-        <v>21.87094179516359</v>
+        <v>21.77234164754228</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.3144860881811485</v>
+        <v>0.317846167476782</v>
       </c>
       <c r="T35">
-        <v>1.320154752211857</v>
+        <v>1.336664072362994</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.861120303244817</v>
+        <v>6.659322647267028</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4322,22 +4322,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.2238095905346761</v>
+        <v>0.2232950619879827</v>
       </c>
       <c r="C36">
-        <v>209.7058660590262</v>
+        <v>208.1393802572776</v>
       </c>
       <c r="D36">
-        <v>283.830842775232</v>
+        <v>284.6536209945483</v>
       </c>
       <c r="E36">
-        <v>-54.09142539028197</v>
+        <v>-51.70216136921709</v>
       </c>
       <c r="F36">
-        <v>81.23497671620588</v>
+        <v>83.62424073727075</v>
       </c>
       <c r="G36">
         <v>7.11</v>
@@ -4358,28 +4358,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M36">
-        <v>4.411059235689979</v>
+        <v>4.540796272033802</v>
       </c>
       <c r="N36">
-        <v>24.96360743097669</v>
+        <v>24.83387039463286</v>
       </c>
       <c r="O36">
-        <v>5.991265783434405</v>
+        <v>5.960128894711887</v>
       </c>
       <c r="P36">
-        <v>18.97234164754228</v>
+        <v>18.87374149992098</v>
       </c>
       <c r="Q36">
-        <v>21.77234164754228</v>
+        <v>21.67374149992098</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.317846167476782</v>
+        <v>0.3213096338276657</v>
       </c>
       <c r="T36">
-        <v>1.336664072362994</v>
+        <v>1.353681371595705</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.659322647267028</v>
+        <v>6.469056285916542</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4404,22 +4404,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2232950619879827</v>
+        <v>0.2227805334412893</v>
       </c>
       <c r="C37">
-        <v>208.1393802572776</v>
+        <v>206.5776785170661</v>
       </c>
       <c r="D37">
-        <v>284.6536209945483</v>
+        <v>285.4811832754017</v>
       </c>
       <c r="E37">
-        <v>-51.70216136921709</v>
+        <v>-49.31289734815222</v>
       </c>
       <c r="F37">
-        <v>83.62424073727075</v>
+        <v>86.01350475833563</v>
       </c>
       <c r="G37">
         <v>7.11</v>
@@ -4440,28 +4440,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M37">
-        <v>4.540796272033802</v>
+        <v>4.670533308377625</v>
       </c>
       <c r="N37">
-        <v>24.83387039463286</v>
+        <v>24.70413335828904</v>
       </c>
       <c r="O37">
-        <v>5.960128894711887</v>
+        <v>5.92899200598937</v>
       </c>
       <c r="P37">
-        <v>18.87374149992098</v>
+        <v>18.77514135229967</v>
       </c>
       <c r="Q37">
-        <v>21.67374149992098</v>
+        <v>21.57514135229967</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.3213096338276657</v>
+        <v>0.3248813335020145</v>
       </c>
       <c r="T37">
-        <v>1.353681371595705</v>
+        <v>1.371230461429437</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.469056285916542</v>
+        <v>6.289360277974416</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4486,22 +4486,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2227805334412893</v>
+        <v>0.2222660048945959</v>
       </c>
       <c r="C38">
-        <v>206.5776785170661</v>
+        <v>205.0208026855948</v>
       </c>
       <c r="D38">
-        <v>285.4811832754017</v>
+        <v>286.3135714649953</v>
       </c>
       <c r="E38">
-        <v>-49.31289734815223</v>
+        <v>-46.92363332708734</v>
       </c>
       <c r="F38">
-        <v>86.01350475833561</v>
+        <v>88.4027687794005</v>
       </c>
       <c r="G38">
         <v>7.11</v>
@@ -4522,28 +4522,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M38">
-        <v>4.670533308377624</v>
+        <v>4.800270344721447</v>
       </c>
       <c r="N38">
-        <v>24.70413335828904</v>
+        <v>24.57439632194522</v>
       </c>
       <c r="O38">
-        <v>5.92899200598937</v>
+        <v>5.897855117266852</v>
       </c>
       <c r="P38">
-        <v>18.77514135229967</v>
+        <v>18.67654120467837</v>
       </c>
       <c r="Q38">
-        <v>21.57514135229967</v>
+        <v>21.47654120467837</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.3248813335020145</v>
+        <v>0.3285664204676125</v>
       </c>
       <c r="T38">
-        <v>1.371230461429437</v>
+        <v>1.389336665226145</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.289360277974417</v>
+        <v>6.119377567758892</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4568,22 +4568,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2222660048945959</v>
+        <v>0.2220402763479025</v>
       </c>
       <c r="C39">
-        <v>205.0208026855948</v>
+        <v>202.9982490880758</v>
       </c>
       <c r="D39">
-        <v>286.3135714649953</v>
+        <v>286.6802818885412</v>
       </c>
       <c r="E39">
-        <v>-46.92363332708734</v>
+        <v>-44.53436930602247</v>
       </c>
       <c r="F39">
-        <v>88.4027687794005</v>
+        <v>90.79203280046538</v>
       </c>
       <c r="G39">
         <v>7.11</v>
@@ -4604,45 +4604,45 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M39">
-        <v>4.800270344721447</v>
+        <v>5.020799413865736</v>
       </c>
       <c r="N39">
-        <v>24.57439632194522</v>
+        <v>24.35386725280093</v>
       </c>
       <c r="O39">
-        <v>5.897855117266852</v>
+        <v>5.844928140672224</v>
       </c>
       <c r="P39">
-        <v>18.67654120467837</v>
+        <v>18.50893911212871</v>
       </c>
       <c r="Q39">
-        <v>21.47654120467837</v>
+        <v>21.30893911212871</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.3285664204676125</v>
+        <v>0.3323703812062943</v>
       </c>
       <c r="T39">
-        <v>1.389336665226145</v>
+        <v>1.40802694011307</v>
       </c>
       <c r="U39">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V39">
         <v>0.24</v>
       </c>
       <c r="W39">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>6.119377567758892</v>
+        <v>5.850595541726653</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4650,22 +4650,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2220402763479025</v>
+        <v>0.2215333478012091</v>
       </c>
       <c r="C40">
-        <v>202.9982490880758</v>
+        <v>201.4359562735676</v>
       </c>
       <c r="D40">
-        <v>286.6802818885412</v>
+        <v>287.5072530950978</v>
       </c>
       <c r="E40">
-        <v>-44.53436930602247</v>
+        <v>-42.14510528495758</v>
       </c>
       <c r="F40">
-        <v>90.79203280046538</v>
+        <v>93.18129682153027</v>
       </c>
       <c r="G40">
         <v>7.11</v>
@@ -4686,28 +4686,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M40">
-        <v>5.020799413865736</v>
+        <v>5.152925714230624</v>
       </c>
       <c r="N40">
-        <v>24.35386725280093</v>
+        <v>24.22174095243604</v>
       </c>
       <c r="O40">
-        <v>5.844928140672224</v>
+        <v>5.813217828584651</v>
       </c>
       <c r="P40">
-        <v>18.50893911212871</v>
+        <v>18.40852312385139</v>
       </c>
       <c r="Q40">
-        <v>21.30893911212871</v>
+        <v>21.20852312385139</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.3323703812062943</v>
+        <v>0.3362990619691952</v>
       </c>
       <c r="T40">
-        <v>1.40802694011307</v>
+        <v>1.427330010897926</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.850595541726653</v>
+        <v>5.700580271425969</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4732,22 +4732,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2215333478012091</v>
+        <v>0.2210264192545157</v>
       </c>
       <c r="C41">
-        <v>201.4359562735676</v>
+        <v>199.8784483004513</v>
       </c>
       <c r="D41">
-        <v>287.5072530950978</v>
+        <v>288.3390091430464</v>
       </c>
       <c r="E41">
-        <v>-42.14510528495758</v>
+        <v>-39.75584126389271</v>
       </c>
       <c r="F41">
-        <v>93.18129682153027</v>
+        <v>95.57056084259514</v>
       </c>
       <c r="G41">
         <v>7.11</v>
@@ -4768,28 +4768,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M41">
-        <v>5.152925714230624</v>
+        <v>5.285052014595512</v>
       </c>
       <c r="N41">
-        <v>24.22174095243604</v>
+        <v>24.08961465207116</v>
       </c>
       <c r="O41">
-        <v>5.813217828584651</v>
+        <v>5.781507516497078</v>
       </c>
       <c r="P41">
-        <v>18.40852312385139</v>
+        <v>18.30810713557408</v>
       </c>
       <c r="Q41">
-        <v>21.20852312385139</v>
+        <v>21.10810713557408</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.3362990619691952</v>
+        <v>0.3403586987575261</v>
       </c>
       <c r="T41">
-        <v>1.427330010897926</v>
+        <v>1.447276517375611</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.700580271425969</v>
+        <v>5.55806576464032</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4814,22 +4814,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2210264192545157</v>
+        <v>0.2205194907078223</v>
       </c>
       <c r="C42">
-        <v>199.8784483004513</v>
+        <v>198.325766816731</v>
       </c>
       <c r="D42">
-        <v>288.3390091430464</v>
+        <v>289.175591680391</v>
       </c>
       <c r="E42">
-        <v>-39.75584126389271</v>
+        <v>-37.36657724282783</v>
       </c>
       <c r="F42">
-        <v>95.57056084259514</v>
+        <v>97.95982486366002</v>
       </c>
       <c r="G42">
         <v>7.11</v>
@@ -4850,28 +4850,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M42">
-        <v>5.285052014595512</v>
+        <v>5.417178314960399</v>
       </c>
       <c r="N42">
-        <v>24.08961465207116</v>
+        <v>23.95748835170627</v>
       </c>
       <c r="O42">
-        <v>5.781507516497078</v>
+        <v>5.749797204409504</v>
       </c>
       <c r="P42">
-        <v>18.30810713557408</v>
+        <v>18.20769114729676</v>
       </c>
       <c r="Q42">
-        <v>21.10810713557408</v>
+        <v>21.00769114729676</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.3403586987575261</v>
+        <v>0.3445559503522411</v>
       </c>
       <c r="T42">
-        <v>1.447276517375611</v>
+        <v>1.467899176615252</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.55806576464032</v>
+        <v>5.422503185014947</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4896,22 +4896,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2205194907078223</v>
+        <v>0.2200125621611289</v>
       </c>
       <c r="C43">
-        <v>198.325766816731</v>
+        <v>196.7779539551649</v>
       </c>
       <c r="D43">
-        <v>289.175591680391</v>
+        <v>290.0170428398898</v>
       </c>
       <c r="E43">
-        <v>-37.36657724282783</v>
+        <v>-34.97731322176294</v>
       </c>
       <c r="F43">
-        <v>97.95982486366002</v>
+        <v>100.3490888847249</v>
       </c>
       <c r="G43">
         <v>7.11</v>
@@ -4932,28 +4932,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M43">
-        <v>5.417178314960399</v>
+        <v>5.549304615325288</v>
       </c>
       <c r="N43">
-        <v>23.95748835170627</v>
+        <v>23.82536205134138</v>
       </c>
       <c r="O43">
-        <v>5.749797204409504</v>
+        <v>5.718086892321931</v>
       </c>
       <c r="P43">
-        <v>18.20769114729676</v>
+        <v>18.10727515901945</v>
       </c>
       <c r="Q43">
-        <v>21.00769114729676</v>
+        <v>20.90727515901945</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.3445559503522411</v>
+        <v>0.348897934760567</v>
       </c>
       <c r="T43">
-        <v>1.467899176615252</v>
+        <v>1.48923296203557</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.422503185014947</v>
+        <v>5.293395966324113</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4978,22 +4978,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2200125621611289</v>
+        <v>0.2195056336144355</v>
       </c>
       <c r="C44">
-        <v>196.7779539551649</v>
+        <v>195.2350523403388</v>
       </c>
       <c r="D44">
-        <v>290.0170428398898</v>
+        <v>290.8634052461285</v>
       </c>
       <c r="E44">
-        <v>-34.97731322176296</v>
+        <v>-32.58804920069808</v>
       </c>
       <c r="F44">
-        <v>100.3490888847249</v>
+        <v>102.7383529057898</v>
       </c>
       <c r="G44">
         <v>7.11</v>
@@ -5014,28 +5014,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M44">
-        <v>5.549304615325287</v>
+        <v>5.681430915690174</v>
       </c>
       <c r="N44">
-        <v>23.82536205134138</v>
+        <v>23.69323575097649</v>
       </c>
       <c r="O44">
-        <v>5.718086892321931</v>
+        <v>5.686376580234358</v>
       </c>
       <c r="P44">
-        <v>18.10727515901945</v>
+        <v>18.00685917074213</v>
       </c>
       <c r="Q44">
-        <v>20.90727515901945</v>
+        <v>20.80685917074213</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.348897934760567</v>
+        <v>0.3533922694990095</v>
       </c>
       <c r="T44">
-        <v>1.489232962035569</v>
+        <v>1.511315301330284</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.293395966324114</v>
+        <v>5.170293734549135</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5060,22 +5060,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2195056336144355</v>
+        <v>0.218998705067742</v>
       </c>
       <c r="C45">
-        <v>195.2350523403388</v>
+        <v>193.6971050958632</v>
       </c>
       <c r="D45">
-        <v>290.8634052461285</v>
+        <v>291.7147220227179</v>
       </c>
       <c r="E45">
-        <v>-32.58804920069808</v>
+        <v>-30.19878517963319</v>
       </c>
       <c r="F45">
-        <v>102.7383529057898</v>
+        <v>105.1276169268547</v>
       </c>
       <c r="G45">
         <v>7.11</v>
@@ -5096,28 +5096,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M45">
-        <v>5.681430915690174</v>
+        <v>5.813557216055063</v>
       </c>
       <c r="N45">
-        <v>23.69323575097649</v>
+        <v>23.5611094506116</v>
       </c>
       <c r="O45">
-        <v>5.686376580234358</v>
+        <v>5.654666268146785</v>
       </c>
       <c r="P45">
-        <v>18.00685917074213</v>
+        <v>17.90644318246482</v>
       </c>
       <c r="Q45">
-        <v>20.80685917074213</v>
+        <v>20.70644318246482</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.3533922694990095</v>
+        <v>0.3580471161923965</v>
       </c>
       <c r="T45">
-        <v>1.511315301330284</v>
+        <v>1.53418629559981</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.170293734549135</v>
+        <v>5.052787058763927</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5142,22 +5142,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.218998705067742</v>
+        <v>0.2184917765210487</v>
       </c>
       <c r="C46">
-        <v>193.6971050958632</v>
+        <v>192.1641558516981</v>
       </c>
       <c r="D46">
-        <v>291.7147220227179</v>
+        <v>292.5710367996176</v>
       </c>
       <c r="E46">
-        <v>-30.19878517963319</v>
+        <v>-27.80952115856832</v>
       </c>
       <c r="F46">
-        <v>105.1276169268547</v>
+        <v>107.5168809479195</v>
       </c>
       <c r="G46">
         <v>7.11</v>
@@ -5178,28 +5178,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M46">
-        <v>5.813557216055063</v>
+        <v>5.94568351641995</v>
       </c>
       <c r="N46">
-        <v>23.5611094506116</v>
+        <v>23.42898315024672</v>
       </c>
       <c r="O46">
-        <v>5.654666268146785</v>
+        <v>5.622955956059212</v>
       </c>
       <c r="P46">
-        <v>17.90644318246482</v>
+        <v>17.8060271941875</v>
       </c>
       <c r="Q46">
-        <v>20.70644318246482</v>
+        <v>20.6060271941875</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.3580471161923965</v>
+        <v>0.3628712300382703</v>
       </c>
       <c r="T46">
-        <v>1.53418629559981</v>
+        <v>1.557888962388228</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.052787058763927</v>
+        <v>4.940502901902507</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5224,22 +5224,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2184917765210487</v>
+        <v>0.2179848479743552</v>
       </c>
       <c r="C47">
-        <v>192.1641558516981</v>
+        <v>190.6362487516064</v>
       </c>
       <c r="D47">
-        <v>292.5710367996176</v>
+        <v>293.4323937205908</v>
       </c>
       <c r="E47">
-        <v>-27.80952115856832</v>
+        <v>-25.42025713750344</v>
       </c>
       <c r="F47">
-        <v>107.5168809479195</v>
+        <v>109.9061449689844</v>
       </c>
       <c r="G47">
         <v>7.11</v>
@@ -5260,28 +5260,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M47">
-        <v>5.94568351641995</v>
+        <v>6.077809816784838</v>
       </c>
       <c r="N47">
-        <v>23.42898315024672</v>
+        <v>23.29685684988183</v>
       </c>
       <c r="O47">
-        <v>5.622955956059212</v>
+        <v>5.591245643971638</v>
       </c>
       <c r="P47">
-        <v>17.8060271941875</v>
+        <v>17.70561120591019</v>
       </c>
       <c r="Q47">
-        <v>20.6060271941875</v>
+        <v>20.50561120591019</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3628712300382703</v>
+        <v>0.3678740147673245</v>
       </c>
       <c r="T47">
-        <v>1.557888962388228</v>
+        <v>1.582469505724365</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.940502901902507</v>
+        <v>4.833100664904626</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5306,22 +5306,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2179848479743552</v>
+        <v>0.2174779194276618</v>
       </c>
       <c r="C48">
-        <v>190.6362487516064</v>
+        <v>189.1134284607396</v>
       </c>
       <c r="D48">
-        <v>293.4323937205908</v>
+        <v>294.2988374507889</v>
       </c>
       <c r="E48">
-        <v>-25.42025713750344</v>
+        <v>-23.03099311643855</v>
       </c>
       <c r="F48">
-        <v>109.9061449689844</v>
+        <v>112.2954089900493</v>
       </c>
       <c r="G48">
         <v>7.11</v>
@@ -5342,28 +5342,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M48">
-        <v>6.077809816784838</v>
+        <v>6.209936117149726</v>
       </c>
       <c r="N48">
-        <v>23.29685684988183</v>
+        <v>23.16473054951694</v>
       </c>
       <c r="O48">
-        <v>5.591245643971638</v>
+        <v>5.559535331884065</v>
       </c>
       <c r="P48">
-        <v>17.70561120591019</v>
+        <v>17.60519521763288</v>
       </c>
       <c r="Q48">
-        <v>20.50561120591019</v>
+        <v>20.40519521763288</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3678740147673245</v>
+        <v>0.373065583825777</v>
       </c>
       <c r="T48">
-        <v>1.582469505724365</v>
+        <v>1.607977616733564</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.833100664904626</v>
+        <v>4.730268735864102</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5388,22 +5388,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2174779194276618</v>
+        <v>0.2169709908809684</v>
       </c>
       <c r="C49">
-        <v>189.1134284607396</v>
+        <v>187.5957401733586</v>
       </c>
       <c r="D49">
-        <v>294.2988374507889</v>
+        <v>295.1704131844728</v>
       </c>
       <c r="E49">
-        <v>-23.03099311643855</v>
+        <v>-20.64172909537368</v>
       </c>
       <c r="F49">
-        <v>112.2954089900493</v>
+        <v>114.6846730111142</v>
       </c>
       <c r="G49">
         <v>7.11</v>
@@ -5424,28 +5424,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M49">
-        <v>6.209936117149726</v>
+        <v>6.342062417514614</v>
       </c>
       <c r="N49">
-        <v>23.16473054951694</v>
+        <v>23.03260424915205</v>
       </c>
       <c r="O49">
-        <v>5.559535331884065</v>
+        <v>5.527825019796492</v>
       </c>
       <c r="P49">
-        <v>17.60519521763288</v>
+        <v>17.50477922935556</v>
       </c>
       <c r="Q49">
-        <v>20.40519521763288</v>
+        <v>20.30477922935556</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.373065583825777</v>
+        <v>0.3784568286172469</v>
       </c>
       <c r="T49">
-        <v>1.607977616733564</v>
+        <v>1.634466808935425</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.730268735864102</v>
+        <v>4.6317214705336</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5470,22 +5470,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2169709908809684</v>
+        <v>0.216464062334275</v>
       </c>
       <c r="C50">
-        <v>187.5957401733586</v>
+        <v>186.0832296206919</v>
       </c>
       <c r="D50">
-        <v>295.1704131844728</v>
+        <v>296.0471666528709</v>
       </c>
       <c r="E50">
-        <v>-20.64172909537369</v>
+        <v>-18.2524650743088</v>
       </c>
       <c r="F50">
-        <v>114.6846730111142</v>
+        <v>117.073937032179</v>
       </c>
       <c r="G50">
         <v>7.11</v>
@@ -5506,28 +5506,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M50">
-        <v>6.342062417514613</v>
+        <v>6.474188717879501</v>
       </c>
       <c r="N50">
-        <v>23.03260424915205</v>
+        <v>22.90047794878716</v>
       </c>
       <c r="O50">
-        <v>5.527825019796492</v>
+        <v>5.496114707708919</v>
       </c>
       <c r="P50">
-        <v>17.50477922935556</v>
+        <v>17.40436324107824</v>
       </c>
       <c r="Q50">
-        <v>20.30477922935556</v>
+        <v>20.20436324107824</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.3784568286172469</v>
+        <v>0.3840594947730883</v>
       </c>
       <c r="T50">
-        <v>1.634466808935425</v>
+        <v>1.661994792988338</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.6317214705336</v>
+        <v>4.537196542563526</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5552,22 +5552,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.216464062334275</v>
+        <v>0.2169071337875816</v>
       </c>
       <c r="C51">
-        <v>186.0832296206919</v>
+        <v>182.9273695759976</v>
       </c>
       <c r="D51">
-        <v>296.0471666528709</v>
+        <v>295.2805706292415</v>
       </c>
       <c r="E51">
-        <v>-18.2524650743088</v>
+        <v>-15.86320105324393</v>
       </c>
       <c r="F51">
-        <v>117.073937032179</v>
+        <v>119.4632010532439</v>
       </c>
       <c r="G51">
         <v>7.11</v>
@@ -5588,45 +5588,45 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M51">
-        <v>6.474188717879501</v>
+        <v>6.904973020877499</v>
       </c>
       <c r="N51">
-        <v>22.90047794878716</v>
+        <v>22.46969364578917</v>
       </c>
       <c r="O51">
-        <v>5.496114707708919</v>
+        <v>5.3927264749894</v>
       </c>
       <c r="P51">
-        <v>17.40436324107824</v>
+        <v>17.07696717079977</v>
       </c>
       <c r="Q51">
-        <v>20.20436324107824</v>
+        <v>19.87696717079977</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.3840594947730883</v>
+        <v>0.3898862675751633</v>
       </c>
       <c r="T51">
-        <v>1.661994792988338</v>
+        <v>1.690623896403369</v>
       </c>
       <c r="U51">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V51">
         <v>0.24</v>
       </c>
       <c r="W51">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>4.537196542563526</v>
+        <v>4.25413199701882</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5634,22 +5634,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2169071337875816</v>
+        <v>0.2164192052408882</v>
       </c>
       <c r="C52">
-        <v>182.9273695759976</v>
+        <v>181.3825346418607</v>
       </c>
       <c r="D52">
-        <v>295.2805706292415</v>
+        <v>296.1249997161694</v>
       </c>
       <c r="E52">
-        <v>-15.86320105324393</v>
+        <v>-13.47393703217905</v>
       </c>
       <c r="F52">
-        <v>119.4632010532439</v>
+        <v>121.8524650743088</v>
       </c>
       <c r="G52">
         <v>7.11</v>
@@ -5670,28 +5670,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M52">
-        <v>6.904973020877499</v>
+        <v>7.043072481295049</v>
       </c>
       <c r="N52">
-        <v>22.46969364578917</v>
+        <v>22.33159418537162</v>
       </c>
       <c r="O52">
-        <v>5.3927264749894</v>
+        <v>5.359582604489188</v>
       </c>
       <c r="P52">
-        <v>17.07696717079977</v>
+        <v>16.97201158088243</v>
       </c>
       <c r="Q52">
-        <v>19.87696717079977</v>
+        <v>19.77201158088243</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3898862675751633</v>
+        <v>0.3959508678385474</v>
       </c>
       <c r="T52">
-        <v>1.690623896403369</v>
+        <v>1.720421534651666</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.25413199701882</v>
+        <v>4.170717644136097</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5716,22 +5716,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2164192052408882</v>
+        <v>0.2159312766941948</v>
       </c>
       <c r="C53">
-        <v>181.3825346418607</v>
+        <v>179.8425432739999</v>
       </c>
       <c r="D53">
-        <v>296.1249997161694</v>
+        <v>296.9742723693735</v>
       </c>
       <c r="E53">
-        <v>-13.47393703217905</v>
+        <v>-11.08467301111416</v>
       </c>
       <c r="F53">
-        <v>121.8524650743088</v>
+        <v>124.2417290953737</v>
       </c>
       <c r="G53">
         <v>7.11</v>
@@ -5752,28 +5752,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M53">
-        <v>7.043072481295049</v>
+        <v>7.181171941712599</v>
       </c>
       <c r="N53">
-        <v>22.33159418537162</v>
+        <v>22.19349472495407</v>
       </c>
       <c r="O53">
-        <v>5.359582604489188</v>
+        <v>5.326438733988976</v>
       </c>
       <c r="P53">
-        <v>16.97201158088243</v>
+        <v>16.86705599096509</v>
       </c>
       <c r="Q53">
-        <v>19.77201158088243</v>
+        <v>19.66705599096509</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3959508678385474</v>
+        <v>0.4022681597795726</v>
       </c>
       <c r="T53">
-        <v>1.720421534651666</v>
+        <v>1.751460741160308</v>
       </c>
       <c r="U53">
         <v>0.0578</v>
@@ -5790,7 +5790,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.170717644136097</v>
+        <v>4.090511535595018</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5798,22 +5798,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2159312766941948</v>
+        <v>0.2154433481475014</v>
       </c>
       <c r="C54">
-        <v>179.8425432739999</v>
+        <v>178.3074372656415</v>
       </c>
       <c r="D54">
-        <v>296.9742723693735</v>
+        <v>297.82843038208</v>
       </c>
       <c r="E54">
-        <v>-11.08467301111416</v>
+        <v>-8.695408990049287</v>
       </c>
       <c r="F54">
-        <v>124.2417290953737</v>
+        <v>126.6309931164386</v>
       </c>
       <c r="G54">
         <v>7.11</v>
@@ -5834,28 +5834,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M54">
-        <v>7.181171941712599</v>
+        <v>7.319271402130149</v>
       </c>
       <c r="N54">
-        <v>22.19349472495407</v>
+        <v>22.05539526453652</v>
       </c>
       <c r="O54">
-        <v>5.326438733988976</v>
+        <v>5.293294863488764</v>
       </c>
       <c r="P54">
-        <v>16.86705599096509</v>
+        <v>16.76210040104775</v>
       </c>
       <c r="Q54">
-        <v>19.66705599096509</v>
+        <v>19.56210040104775</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.4022681597795726</v>
+        <v>0.4088542726542583</v>
       </c>
       <c r="T54">
-        <v>1.751460741160308</v>
+        <v>1.783820764967191</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.090511535595018</v>
+        <v>4.013332072659264</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5880,22 +5880,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2154433481475014</v>
+        <v>0.216391819600808</v>
       </c>
       <c r="C55">
-        <v>178.3074372656415</v>
+        <v>174.2622804540458</v>
       </c>
       <c r="D55">
-        <v>297.82843038208</v>
+        <v>296.1725375915492</v>
       </c>
       <c r="E55">
-        <v>-8.695408990049287</v>
+        <v>-6.306144968984398</v>
       </c>
       <c r="F55">
-        <v>126.6309931164386</v>
+        <v>129.0202571375034</v>
       </c>
       <c r="G55">
         <v>7.11</v>
@@ -5916,45 +5916,45 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M55">
-        <v>7.319271402130149</v>
+        <v>7.908941762528961</v>
       </c>
       <c r="N55">
-        <v>22.05539526453652</v>
+        <v>21.4657249041377</v>
       </c>
       <c r="O55">
-        <v>5.293294863488764</v>
+        <v>5.151773976993049</v>
       </c>
       <c r="P55">
-        <v>16.76210040104775</v>
+        <v>16.31395092714466</v>
       </c>
       <c r="Q55">
-        <v>19.56210040104775</v>
+        <v>19.11395092714466</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.4088542726542583</v>
+        <v>0.4157267382626261</v>
       </c>
       <c r="T55">
-        <v>1.783820764967191</v>
+        <v>1.817587746330894</v>
       </c>
       <c r="U55">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V55">
         <v>0.24</v>
       </c>
       <c r="W55">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>4.013332072659264</v>
+        <v>3.714108353387828</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5962,22 +5962,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.216391819600808</v>
+        <v>0.2159304910541146</v>
       </c>
       <c r="C56">
-        <v>174.2622804540458</v>
+        <v>172.6761225986719</v>
       </c>
       <c r="D56">
-        <v>296.1725375915492</v>
+        <v>296.9756437572402</v>
       </c>
       <c r="E56">
-        <v>-6.306144968984398</v>
+        <v>-3.916880947919537</v>
       </c>
       <c r="F56">
-        <v>129.0202571375034</v>
+        <v>131.4095211585683</v>
       </c>
       <c r="G56">
         <v>7.11</v>
@@ -5998,28 +5998,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M56">
-        <v>7.908941762528961</v>
+        <v>8.055403647020237</v>
       </c>
       <c r="N56">
-        <v>21.4657249041377</v>
+        <v>21.31926301964643</v>
       </c>
       <c r="O56">
-        <v>5.151773976993049</v>
+        <v>5.116623124715143</v>
       </c>
       <c r="P56">
-        <v>16.31395092714466</v>
+        <v>16.20263989493128</v>
       </c>
       <c r="Q56">
-        <v>19.11395092714466</v>
+        <v>19.00263989493128</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.4157267382626261</v>
+        <v>0.4229046467869214</v>
       </c>
       <c r="T56">
-        <v>1.817587746330894</v>
+        <v>1.852855482421874</v>
       </c>
       <c r="U56">
         <v>0.0613</v>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.714108353387828</v>
+        <v>3.646579110598959</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6044,22 +6044,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2159304910541146</v>
+        <v>0.2154691625074212</v>
       </c>
       <c r="C57">
-        <v>172.6761225986719</v>
+        <v>171.0943320165819</v>
       </c>
       <c r="D57">
-        <v>296.9756437572402</v>
+        <v>297.7831171962151</v>
       </c>
       <c r="E57">
-        <v>-3.916880947919537</v>
+        <v>-1.527616926854648</v>
       </c>
       <c r="F57">
-        <v>131.4095211585683</v>
+        <v>133.7987851796332</v>
       </c>
       <c r="G57">
         <v>7.11</v>
@@ -6080,28 +6080,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M57">
-        <v>8.055403647020237</v>
+        <v>8.201865531511515</v>
       </c>
       <c r="N57">
-        <v>21.31926301964643</v>
+        <v>21.17280113515515</v>
       </c>
       <c r="O57">
-        <v>5.116623124715143</v>
+        <v>5.081472272437236</v>
       </c>
       <c r="P57">
-        <v>16.20263989493128</v>
+        <v>16.09132886271792</v>
       </c>
       <c r="Q57">
-        <v>19.00263989493128</v>
+        <v>18.89132886271792</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.4229046467869214</v>
+        <v>0.4304088238805027</v>
       </c>
       <c r="T57">
-        <v>1.852855482421874</v>
+        <v>1.88972629742608</v>
       </c>
       <c r="U57">
         <v>0.0613</v>
@@ -6118,7 +6118,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.646579110598959</v>
+        <v>3.58146162648112</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6126,22 +6126,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2154691625074212</v>
+        <v>0.2150078339607278</v>
       </c>
       <c r="C58">
-        <v>171.0943320165819</v>
+        <v>169.5169444286014</v>
       </c>
       <c r="D58">
-        <v>297.7831171962151</v>
+        <v>298.5949936292995</v>
       </c>
       <c r="E58">
-        <v>-1.527616926854648</v>
+        <v>0.861647094210241</v>
       </c>
       <c r="F58">
-        <v>133.7987851796332</v>
+        <v>136.1880492006981</v>
       </c>
       <c r="G58">
         <v>7.11</v>
@@ -6162,28 +6162,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M58">
-        <v>8.201865531511515</v>
+        <v>8.348327416002792</v>
       </c>
       <c r="N58">
-        <v>21.17280113515515</v>
+        <v>21.02633925066387</v>
       </c>
       <c r="O58">
-        <v>5.081472272437236</v>
+        <v>5.046321420159329</v>
       </c>
       <c r="P58">
-        <v>16.09132886271792</v>
+        <v>15.98001783050454</v>
       </c>
       <c r="Q58">
-        <v>18.89132886271792</v>
+        <v>18.78001783050454</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.4304088238805027</v>
+        <v>0.4382620324668088</v>
       </c>
       <c r="T58">
-        <v>1.88972629742608</v>
+        <v>1.928312034058388</v>
       </c>
       <c r="U58">
         <v>0.0613</v>
@@ -6200,7 +6200,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.58146162648112</v>
+        <v>3.518628966367416</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6208,22 +6208,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2150078339607278</v>
+        <v>0.2157807454140343</v>
       </c>
       <c r="C59">
-        <v>169.5169444286014</v>
+        <v>165.7699531548766</v>
       </c>
       <c r="D59">
-        <v>298.5949936292995</v>
+        <v>297.2372663766395</v>
       </c>
       <c r="E59">
-        <v>0.861647094210241</v>
+        <v>3.25091111527513</v>
       </c>
       <c r="F59">
-        <v>136.1880492006981</v>
+        <v>138.577313221763</v>
       </c>
       <c r="G59">
         <v>7.11</v>
@@ -6244,45 +6244,45 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M59">
-        <v>8.348327416002792</v>
+        <v>8.882805777515008</v>
       </c>
       <c r="N59">
-        <v>21.02633925066387</v>
+        <v>20.49186088915166</v>
       </c>
       <c r="O59">
-        <v>5.046321420159329</v>
+        <v>4.918046613396398</v>
       </c>
       <c r="P59">
-        <v>15.98001783050454</v>
+        <v>15.57381427575526</v>
       </c>
       <c r="Q59">
-        <v>18.78001783050454</v>
+        <v>18.37381427575526</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.4382620324668088</v>
+        <v>0.4464892033667485</v>
       </c>
       <c r="T59">
-        <v>1.928312034058388</v>
+        <v>1.968735186720806</v>
       </c>
       <c r="U59">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V59">
         <v>0.24</v>
       </c>
       <c r="W59">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y59">
-        <v>3.518628966367416</v>
+        <v>3.306913086068208</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6290,22 +6290,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2157807454140344</v>
+        <v>0.215340696867341</v>
       </c>
       <c r="C60">
-        <v>165.7699531548765</v>
+        <v>164.152178395735</v>
       </c>
       <c r="D60">
-        <v>297.2372663766394</v>
+        <v>298.0087556385628</v>
       </c>
       <c r="E60">
-        <v>3.250911115275102</v>
+        <v>5.640175136339963</v>
       </c>
       <c r="F60">
-        <v>138.5773132217629</v>
+        <v>140.9665772428278</v>
       </c>
       <c r="G60">
         <v>7.11</v>
@@ -6326,28 +6326,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M60">
-        <v>8.882805777515006</v>
+        <v>9.035957601265263</v>
       </c>
       <c r="N60">
-        <v>20.49186088915166</v>
+        <v>20.3387090654014</v>
       </c>
       <c r="O60">
-        <v>4.918046613396398</v>
+        <v>4.881290175696336</v>
       </c>
       <c r="P60">
-        <v>15.57381427575526</v>
+        <v>15.45741888970507</v>
       </c>
       <c r="Q60">
-        <v>18.37381427575526</v>
+        <v>18.25741888970507</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.4464892033667485</v>
+        <v>0.4551176996764414</v>
       </c>
       <c r="T60">
-        <v>1.968735186720806</v>
+        <v>2.011130200488708</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.306913086068209</v>
+        <v>3.250863711728071</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6372,22 +6372,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.215340696867341</v>
+        <v>0.2149006483206475</v>
       </c>
       <c r="C61">
-        <v>164.152178395735</v>
+        <v>162.5384189107143</v>
       </c>
       <c r="D61">
-        <v>298.0087556385628</v>
+        <v>298.784260174607</v>
       </c>
       <c r="E61">
-        <v>5.640175136339963</v>
+        <v>8.029439157404852</v>
       </c>
       <c r="F61">
-        <v>140.9665772428278</v>
+        <v>143.3558412638927</v>
       </c>
       <c r="G61">
         <v>7.11</v>
@@ -6408,28 +6408,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M61">
-        <v>9.035957601265263</v>
+        <v>9.189109425015523</v>
       </c>
       <c r="N61">
-        <v>20.3387090654014</v>
+        <v>20.18555724165114</v>
       </c>
       <c r="O61">
-        <v>4.881290175696336</v>
+        <v>4.844533737996274</v>
       </c>
       <c r="P61">
-        <v>15.45741888970507</v>
+        <v>15.34102350365487</v>
       </c>
       <c r="Q61">
-        <v>18.25741888970507</v>
+        <v>18.14102350365487</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.4551176996764414</v>
+        <v>0.4641776208016188</v>
       </c>
       <c r="T61">
-        <v>2.011130200488708</v>
+        <v>2.055644964945005</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.250863711728071</v>
+        <v>3.196682649865935</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6454,22 +6454,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2149006483206475</v>
+        <v>0.2144605997739542</v>
       </c>
       <c r="C62">
-        <v>162.5384189107143</v>
+        <v>160.9287061282961</v>
       </c>
       <c r="D62">
-        <v>298.784260174607</v>
+        <v>299.5638114132537</v>
       </c>
       <c r="E62">
-        <v>8.029439157404852</v>
+        <v>10.41870317846974</v>
       </c>
       <c r="F62">
-        <v>143.3558412638927</v>
+        <v>145.7451052849576</v>
       </c>
       <c r="G62">
         <v>7.11</v>
@@ -6490,28 +6490,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M62">
-        <v>9.189109425015523</v>
+        <v>9.342261248765782</v>
       </c>
       <c r="N62">
-        <v>20.18555724165114</v>
+        <v>20.03240541790088</v>
       </c>
       <c r="O62">
-        <v>4.844533737996274</v>
+        <v>4.807777300296212</v>
       </c>
       <c r="P62">
-        <v>15.34102350365487</v>
+        <v>15.22462811760467</v>
       </c>
       <c r="Q62">
-        <v>18.14102350365487</v>
+        <v>18.02462811760467</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.4641776208016188</v>
+        <v>0.4737021532665492</v>
       </c>
       <c r="T62">
-        <v>2.055644964945005</v>
+        <v>2.102442537834959</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.196682649865935</v>
+        <v>3.144278016261576</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6536,22 +6536,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2144605997739542</v>
+        <v>0.2140205512272608</v>
       </c>
       <c r="C63">
-        <v>160.9287061282961</v>
+        <v>159.3230718058181</v>
       </c>
       <c r="D63">
-        <v>299.5638114132537</v>
+        <v>300.3474411118406</v>
       </c>
       <c r="E63">
-        <v>10.41870317846974</v>
+        <v>12.8079671995346</v>
       </c>
       <c r="F63">
-        <v>145.7451052849576</v>
+        <v>148.1343693060224</v>
       </c>
       <c r="G63">
         <v>7.11</v>
@@ -6572,28 +6572,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M63">
-        <v>9.342261248765782</v>
+        <v>9.49541307251604</v>
       </c>
       <c r="N63">
-        <v>20.03240541790088</v>
+        <v>19.87925359415063</v>
       </c>
       <c r="O63">
-        <v>4.807777300296212</v>
+        <v>4.77102086259615</v>
       </c>
       <c r="P63">
-        <v>15.22462811760467</v>
+        <v>15.10823273155448</v>
       </c>
       <c r="Q63">
-        <v>18.02462811760467</v>
+        <v>17.90823273155448</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.4737021532665492</v>
+        <v>0.4837279769138442</v>
       </c>
       <c r="T63">
-        <v>2.102442537834959</v>
+        <v>2.151703140877015</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.144278016261576</v>
+        <v>3.09356385470897</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6618,22 +6618,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2140205512272608</v>
+        <v>0.2135805026805674</v>
       </c>
       <c r="C64">
-        <v>159.3230718058181</v>
+        <v>157.7215480337856</v>
       </c>
       <c r="D64">
-        <v>300.3474411118406</v>
+        <v>301.1351813608729</v>
       </c>
       <c r="E64">
-        <v>12.8079671995346</v>
+        <v>15.19723122059949</v>
       </c>
       <c r="F64">
-        <v>148.1343693060224</v>
+        <v>150.5236333270873</v>
       </c>
       <c r="G64">
         <v>7.11</v>
@@ -6654,28 +6654,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M64">
-        <v>9.49541307251604</v>
+        <v>9.648564896266299</v>
       </c>
       <c r="N64">
-        <v>19.87925359415063</v>
+        <v>19.72610177040037</v>
       </c>
       <c r="O64">
-        <v>4.77102086259615</v>
+        <v>4.734264424896089</v>
       </c>
       <c r="P64">
-        <v>15.10823273155448</v>
+        <v>14.99183734550428</v>
       </c>
       <c r="Q64">
-        <v>17.90823273155448</v>
+        <v>17.79183734550428</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.4837279769138442</v>
+        <v>0.4942957369745064</v>
       </c>
       <c r="T64">
-        <v>2.151703140877015</v>
+        <v>2.203626479218642</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6692,7 +6692,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.09356385470897</v>
+        <v>3.044459666538986</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6700,22 +6700,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2135805026805674</v>
+        <v>0.2169343741338739</v>
       </c>
       <c r="C65">
-        <v>157.7215480337856</v>
+        <v>149.430671940546</v>
       </c>
       <c r="D65">
-        <v>301.1351813608729</v>
+        <v>295.2335692886982</v>
       </c>
       <c r="E65">
-        <v>15.19723122059949</v>
+        <v>17.58649524166438</v>
       </c>
       <c r="F65">
-        <v>150.5236333270873</v>
+        <v>152.9128973481522</v>
       </c>
       <c r="G65">
         <v>7.11</v>
@@ -6736,45 +6736,45 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M65">
-        <v>9.648564896266299</v>
+        <v>10.99443731933215</v>
       </c>
       <c r="N65">
-        <v>19.72610177040037</v>
+        <v>18.38022934733452</v>
       </c>
       <c r="O65">
-        <v>4.734264424896089</v>
+        <v>4.411255043360285</v>
       </c>
       <c r="P65">
-        <v>14.99183734550428</v>
+        <v>13.96897430397424</v>
       </c>
       <c r="Q65">
-        <v>17.79183734550428</v>
+        <v>16.76897430397424</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.4942957369745064</v>
+        <v>0.5054505948163165</v>
       </c>
       <c r="T65">
-        <v>2.203626479218642</v>
+        <v>2.258434447468137</v>
       </c>
       <c r="U65">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V65">
         <v>0.24</v>
       </c>
       <c r="W65">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y65">
-        <v>3.044459666538986</v>
+        <v>2.671775354525467</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6782,22 +6782,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2169343741338739</v>
+        <v>0.2165536055871806</v>
       </c>
       <c r="C66">
-        <v>149.430671940546</v>
+        <v>147.6997580417323</v>
       </c>
       <c r="D66">
-        <v>295.2335692886982</v>
+        <v>295.8919194109494</v>
       </c>
       <c r="E66">
-        <v>17.58649524166438</v>
+        <v>19.97575926272924</v>
       </c>
       <c r="F66">
-        <v>152.9128973481522</v>
+        <v>155.3021613692171</v>
       </c>
       <c r="G66">
         <v>7.11</v>
@@ -6818,28 +6818,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M66">
-        <v>10.99443731933215</v>
+        <v>11.16622540244671</v>
       </c>
       <c r="N66">
-        <v>18.38022934733452</v>
+        <v>18.20844126421996</v>
       </c>
       <c r="O66">
-        <v>4.411255043360285</v>
+        <v>4.370025903412789</v>
       </c>
       <c r="P66">
-        <v>13.96897430397424</v>
+        <v>13.83841536080717</v>
       </c>
       <c r="Q66">
-        <v>16.76897430397424</v>
+        <v>16.63841536080717</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.5054505948163165</v>
+        <v>0.5172428731062302</v>
       </c>
       <c r="T66">
-        <v>2.258434447468137</v>
+        <v>2.316374299617603</v>
       </c>
       <c r="U66">
         <v>0.07190000000000001</v>
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.671775354525467</v>
+        <v>2.630671118301998</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6864,22 +6864,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2165536055871806</v>
+        <v>0.2161728370404871</v>
       </c>
       <c r="C67">
-        <v>147.6997580417323</v>
+        <v>145.9717868540178</v>
       </c>
       <c r="D67">
-        <v>295.8919194109494</v>
+        <v>296.5532122442998</v>
       </c>
       <c r="E67">
-        <v>19.97575926272924</v>
+        <v>22.36502328379413</v>
       </c>
       <c r="F67">
-        <v>155.3021613692171</v>
+        <v>157.691425390282</v>
       </c>
       <c r="G67">
         <v>7.11</v>
@@ -6900,28 +6900,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M67">
-        <v>11.16622540244671</v>
+        <v>11.33801348556127</v>
       </c>
       <c r="N67">
-        <v>18.20844126421996</v>
+        <v>18.03665318110539</v>
       </c>
       <c r="O67">
-        <v>4.370025903412789</v>
+        <v>4.328796763465294</v>
       </c>
       <c r="P67">
-        <v>13.83841536080717</v>
+        <v>13.7078564176401</v>
       </c>
       <c r="Q67">
-        <v>16.63841536080717</v>
+        <v>16.5078564176401</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.5172428731062302</v>
+        <v>0.5297288148249621</v>
       </c>
       <c r="T67">
-        <v>2.316374299617603</v>
+        <v>2.377722378364096</v>
       </c>
       <c r="U67">
         <v>0.07190000000000001</v>
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.630671118301998</v>
+        <v>2.590812464994392</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6946,22 +6946,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2161728370404871</v>
+        <v>0.2157920684937937</v>
       </c>
       <c r="C68">
-        <v>145.9717868540178</v>
+        <v>144.24677815171</v>
       </c>
       <c r="D68">
-        <v>296.5532122442998</v>
+        <v>297.2174675630569</v>
       </c>
       <c r="E68">
-        <v>22.36502328379413</v>
+        <v>24.75428730485902</v>
       </c>
       <c r="F68">
-        <v>157.691425390282</v>
+        <v>160.0806894113469</v>
       </c>
       <c r="G68">
         <v>7.11</v>
@@ -6982,28 +6982,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M68">
-        <v>11.33801348556127</v>
+        <v>11.50980156867584</v>
       </c>
       <c r="N68">
-        <v>18.03665318110539</v>
+        <v>17.86486509799083</v>
       </c>
       <c r="O68">
-        <v>4.328796763465294</v>
+        <v>4.287567623517798</v>
       </c>
       <c r="P68">
-        <v>13.7078564176401</v>
+        <v>13.57729747447303</v>
       </c>
       <c r="Q68">
-        <v>16.5078564176401</v>
+        <v>16.37729747447303</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.5297288148249621</v>
+        <v>0.5429714802842235</v>
       </c>
       <c r="T68">
-        <v>2.377722378364096</v>
+        <v>2.442788522489165</v>
       </c>
       <c r="U68">
         <v>0.07190000000000001</v>
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.590812464994392</v>
+        <v>2.552143622233282</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7028,22 +7028,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2157920684937937</v>
+        <v>0.2154112999471003</v>
       </c>
       <c r="C69">
-        <v>144.24677815171</v>
+        <v>142.524751886686</v>
       </c>
       <c r="D69">
-        <v>297.2174675630569</v>
+        <v>297.8847053190977</v>
       </c>
       <c r="E69">
-        <v>24.75428730485902</v>
+        <v>27.14355132592391</v>
       </c>
       <c r="F69">
-        <v>160.0806894113469</v>
+        <v>162.4699534324118</v>
       </c>
       <c r="G69">
         <v>7.11</v>
@@ -7064,28 +7064,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M69">
-        <v>11.50980156867584</v>
+        <v>11.68158965179041</v>
       </c>
       <c r="N69">
-        <v>17.86486509799083</v>
+        <v>17.69307701487626</v>
       </c>
       <c r="O69">
-        <v>4.287567623517798</v>
+        <v>4.246338483570302</v>
       </c>
       <c r="P69">
-        <v>13.57729747447303</v>
+        <v>13.44673853130596</v>
       </c>
       <c r="Q69">
-        <v>16.37729747447303</v>
+        <v>16.24673853130596</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.5429714802842235</v>
+        <v>0.5570418123346885</v>
       </c>
       <c r="T69">
-        <v>2.442788522489165</v>
+        <v>2.511921300622051</v>
       </c>
       <c r="U69">
         <v>0.07190000000000001</v>
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.552143622233282</v>
+        <v>2.51461209837691</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7110,22 +7110,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2154112999471003</v>
+        <v>0.2170756914004069</v>
       </c>
       <c r="C70">
-        <v>142.524751886686</v>
+        <v>137.2407585928909</v>
       </c>
       <c r="D70">
-        <v>297.8847053190977</v>
+        <v>294.9899760463675</v>
       </c>
       <c r="E70">
-        <v>27.14355132592391</v>
+        <v>29.53281534698877</v>
       </c>
       <c r="F70">
-        <v>162.4699534324118</v>
+        <v>164.8592174534766</v>
       </c>
       <c r="G70">
         <v>7.11</v>
@@ -7146,45 +7146,45 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M70">
-        <v>11.68158965179041</v>
+        <v>12.49632868297353</v>
       </c>
       <c r="N70">
-        <v>17.69307701487626</v>
+        <v>16.87833798369314</v>
       </c>
       <c r="O70">
-        <v>4.246338483570302</v>
+        <v>4.050801116086353</v>
       </c>
       <c r="P70">
-        <v>13.44673853130596</v>
+        <v>12.82753686760678</v>
       </c>
       <c r="Q70">
-        <v>16.24673853130596</v>
+        <v>15.62753686760678</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.5570418123346885</v>
+        <v>0.5720199077432483</v>
       </c>
       <c r="T70">
-        <v>2.511921300622051</v>
+        <v>2.585514257989317</v>
       </c>
       <c r="U70">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V70">
         <v>0.24</v>
       </c>
       <c r="W70">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y70">
-        <v>2.51461209837691</v>
+        <v>2.350663735877096</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7192,22 +7192,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2170756914004069</v>
+        <v>0.2167245628537135</v>
       </c>
       <c r="C71">
-        <v>137.2407585928909</v>
+        <v>135.4574894028143</v>
       </c>
       <c r="D71">
-        <v>294.9899760463675</v>
+        <v>295.5959708773558</v>
       </c>
       <c r="E71">
-        <v>29.53281534698877</v>
+        <v>31.92207936805366</v>
       </c>
       <c r="F71">
-        <v>164.8592174534766</v>
+        <v>167.2484814745415</v>
       </c>
       <c r="G71">
         <v>7.11</v>
@@ -7228,28 +7228,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M71">
-        <v>12.49632868297353</v>
+        <v>12.67743489577025</v>
       </c>
       <c r="N71">
-        <v>16.87833798369314</v>
+        <v>16.69723177089642</v>
       </c>
       <c r="O71">
-        <v>4.050801116086353</v>
+        <v>4.00733562501514</v>
       </c>
       <c r="P71">
-        <v>12.82753686760678</v>
+        <v>12.68989614588128</v>
       </c>
       <c r="Q71">
-        <v>15.62753686760678</v>
+        <v>15.48989614588128</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.5720199077432483</v>
+        <v>0.5879965428457118</v>
       </c>
       <c r="T71">
-        <v>2.585514257989317</v>
+        <v>2.6640134125144</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.350663735877096</v>
+        <v>2.317082825364566</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7274,22 +7274,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2167245628537135</v>
+        <v>0.2163734343070202</v>
       </c>
       <c r="C72">
-        <v>135.4574894028143</v>
+        <v>133.6767151157121</v>
       </c>
       <c r="D72">
-        <v>295.5959708773558</v>
+        <v>296.2044606113185</v>
       </c>
       <c r="E72">
-        <v>31.92207936805366</v>
+        <v>34.31134338911855</v>
       </c>
       <c r="F72">
-        <v>167.2484814745415</v>
+        <v>169.6377454956064</v>
       </c>
       <c r="G72">
         <v>7.11</v>
@@ -7310,28 +7310,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M72">
-        <v>12.67743489577025</v>
+        <v>12.85854110856697</v>
       </c>
       <c r="N72">
-        <v>16.69723177089642</v>
+        <v>16.5161255580997</v>
       </c>
       <c r="O72">
-        <v>4.00733562501514</v>
+        <v>3.963870133943928</v>
       </c>
       <c r="P72">
-        <v>12.68989614588128</v>
+        <v>12.55225542415577</v>
       </c>
       <c r="Q72">
-        <v>15.48989614588128</v>
+        <v>15.35225542415577</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.5879965428457118</v>
+        <v>0.6050750148517937</v>
       </c>
       <c r="T72">
-        <v>2.6640134125144</v>
+        <v>2.747926301834317</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.317082825364566</v>
+        <v>2.284447855993234</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7356,22 +7356,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2163734343070201</v>
+        <v>0.2160223057603267</v>
       </c>
       <c r="C73">
-        <v>133.6767151157121</v>
+        <v>131.8984511707772</v>
       </c>
       <c r="D73">
-        <v>296.2044606113185</v>
+        <v>296.8154606874484</v>
       </c>
       <c r="E73">
-        <v>34.31134338911852</v>
+        <v>36.70060741018338</v>
       </c>
       <c r="F73">
-        <v>169.6377454956064</v>
+        <v>172.0270095166712</v>
       </c>
       <c r="G73">
         <v>7.11</v>
@@ -7392,28 +7392,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M73">
-        <v>12.85854110856696</v>
+        <v>13.03964732136368</v>
       </c>
       <c r="N73">
-        <v>16.5161255580997</v>
+        <v>16.33501934530299</v>
       </c>
       <c r="O73">
-        <v>3.963870133943928</v>
+        <v>3.920404642872716</v>
       </c>
       <c r="P73">
-        <v>12.55225542415577</v>
+        <v>12.41461470243027</v>
       </c>
       <c r="Q73">
-        <v>15.35225542415577</v>
+        <v>15.21461470243027</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.6050750148517935</v>
+        <v>0.6233733777154525</v>
       </c>
       <c r="T73">
-        <v>2.747926301834316</v>
+        <v>2.837832968962798</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.284447855993234</v>
+        <v>2.252719413548884</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7438,22 +7438,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2160223057603267</v>
+        <v>0.2156711772136333</v>
       </c>
       <c r="C74">
-        <v>131.8984511707772</v>
+        <v>130.1227131348548</v>
       </c>
       <c r="D74">
-        <v>296.8154606874484</v>
+        <v>297.428986672591</v>
       </c>
       <c r="E74">
-        <v>36.70060741018338</v>
+        <v>39.08987143124827</v>
       </c>
       <c r="F74">
-        <v>172.0270095166712</v>
+        <v>174.4162735377361</v>
       </c>
       <c r="G74">
         <v>7.11</v>
@@ -7474,28 +7474,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M74">
-        <v>13.03964732136368</v>
+        <v>13.2207535341604</v>
       </c>
       <c r="N74">
-        <v>16.33501934530299</v>
+        <v>16.15391313250627</v>
       </c>
       <c r="O74">
-        <v>3.920404642872716</v>
+        <v>3.876939151801504</v>
       </c>
       <c r="P74">
-        <v>12.41461470243027</v>
+        <v>12.27697398070476</v>
       </c>
       <c r="Q74">
-        <v>15.21461470243027</v>
+        <v>15.07697398070476</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.6233733777154525</v>
+        <v>0.6430271748653085</v>
       </c>
       <c r="T74">
-        <v>2.837832968962798</v>
+        <v>2.934399389211908</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.252719413548884</v>
+        <v>2.221860243500269</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7520,22 +7520,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2156711772136333</v>
+        <v>0.2153200486669399</v>
       </c>
       <c r="C75">
-        <v>130.1227131348548</v>
+        <v>128.3495167037659</v>
       </c>
       <c r="D75">
-        <v>297.428986672591</v>
+        <v>298.0450542625669</v>
       </c>
       <c r="E75">
-        <v>39.08987143124827</v>
+        <v>41.47913545231316</v>
       </c>
       <c r="F75">
-        <v>174.4162735377361</v>
+        <v>176.805537558801</v>
       </c>
       <c r="G75">
         <v>7.11</v>
@@ -7556,28 +7556,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M75">
-        <v>13.2207535341604</v>
+        <v>13.40185974695712</v>
       </c>
       <c r="N75">
-        <v>16.15391313250627</v>
+        <v>15.97280691970955</v>
       </c>
       <c r="O75">
-        <v>3.876939151801504</v>
+        <v>3.833473660730292</v>
       </c>
       <c r="P75">
-        <v>12.27697398070476</v>
+        <v>12.13933325897926</v>
       </c>
       <c r="Q75">
-        <v>15.07697398070476</v>
+        <v>14.93933325897926</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.6430271748653085</v>
+        <v>0.6641928025651533</v>
       </c>
       <c r="T75">
-        <v>2.934399389211908</v>
+        <v>3.038393995634026</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7594,7 +7594,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.221860243500269</v>
+        <v>2.19183510507459</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7602,22 +7602,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2153200486669399</v>
+        <v>0.2149689201202465</v>
       </c>
       <c r="C76">
-        <v>128.3495167037659</v>
+        <v>126.5788777036443</v>
       </c>
       <c r="D76">
-        <v>298.0450542625669</v>
+        <v>298.6636792835102</v>
       </c>
       <c r="E76">
-        <v>41.47913545231316</v>
+        <v>43.86839947337805</v>
       </c>
       <c r="F76">
-        <v>176.805537558801</v>
+        <v>179.1948015798659</v>
       </c>
       <c r="G76">
         <v>7.11</v>
@@ -7638,28 +7638,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M76">
-        <v>13.40185974695712</v>
+        <v>13.58296595975384</v>
       </c>
       <c r="N76">
-        <v>15.97280691970955</v>
+        <v>15.79170070691283</v>
       </c>
       <c r="O76">
-        <v>3.833473660730292</v>
+        <v>3.790008169659079</v>
       </c>
       <c r="P76">
-        <v>12.13933325897926</v>
+        <v>12.00169253725375</v>
       </c>
       <c r="Q76">
-        <v>14.93933325897926</v>
+        <v>14.80169253725375</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.6641928025651533</v>
+        <v>0.6870516804809861</v>
       </c>
       <c r="T76">
-        <v>3.038393995634026</v>
+        <v>3.150708170569915</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.19183510507459</v>
+        <v>2.162610637006928</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7684,22 +7684,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2149689201202465</v>
+        <v>0.2146177915735531</v>
       </c>
       <c r="C77">
-        <v>126.5788777036443</v>
+        <v>124.8108120922936</v>
       </c>
       <c r="D77">
-        <v>298.6636792835102</v>
+        <v>299.2848776932244</v>
       </c>
       <c r="E77">
-        <v>43.86839947337805</v>
+        <v>46.25766349444291</v>
       </c>
       <c r="F77">
-        <v>179.1948015798659</v>
+        <v>181.5840656009308</v>
       </c>
       <c r="G77">
         <v>7.11</v>
@@ -7720,28 +7720,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M77">
-        <v>13.58296595975384</v>
+        <v>13.76407217255055</v>
       </c>
       <c r="N77">
-        <v>15.79170070691283</v>
+        <v>15.61059449411611</v>
       </c>
       <c r="O77">
-        <v>3.790008169659079</v>
+        <v>3.746542678587867</v>
       </c>
       <c r="P77">
-        <v>12.00169253725375</v>
+        <v>11.86405181552825</v>
       </c>
       <c r="Q77">
-        <v>14.80169253725375</v>
+        <v>14.66405181552825</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.6870516804809861</v>
+        <v>0.7118154648898046</v>
       </c>
       <c r="T77">
-        <v>3.150708170569915</v>
+        <v>3.272381860083794</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7758,7 +7758,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.162610637006928</v>
+        <v>2.134155233888416</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7766,22 +7766,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2146177915735531</v>
+        <v>0.2142666630268597</v>
       </c>
       <c r="C78">
-        <v>124.8108120922936</v>
+        <v>123.0453359605572</v>
       </c>
       <c r="D78">
-        <v>299.2848776932244</v>
+        <v>299.9086655825528</v>
       </c>
       <c r="E78">
-        <v>46.25766349444291</v>
+        <v>48.6469275155078</v>
       </c>
       <c r="F78">
-        <v>181.5840656009308</v>
+        <v>183.9733296219956</v>
       </c>
       <c r="G78">
         <v>7.11</v>
@@ -7802,28 +7802,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M78">
-        <v>13.76407217255055</v>
+        <v>13.94517838534727</v>
       </c>
       <c r="N78">
-        <v>15.61059449411611</v>
+        <v>15.4294882813194</v>
       </c>
       <c r="O78">
-        <v>3.746542678587867</v>
+        <v>3.703077187516655</v>
       </c>
       <c r="P78">
-        <v>11.86405181552825</v>
+        <v>11.72641109380274</v>
       </c>
       <c r="Q78">
-        <v>14.66405181552825</v>
+        <v>14.52641109380274</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.7118154648898046</v>
+        <v>0.7387326218559117</v>
       </c>
       <c r="T78">
-        <v>3.272381860083794</v>
+        <v>3.404635870424966</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.134155233888416</v>
+        <v>2.106438932149605</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7848,22 +7848,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2142666630268597</v>
+        <v>0.2139155344801663</v>
       </c>
       <c r="C79">
-        <v>123.0453359605572</v>
+        <v>121.2824655337094</v>
       </c>
       <c r="D79">
-        <v>299.9086655825528</v>
+        <v>300.5350591767699</v>
       </c>
       <c r="E79">
-        <v>48.6469275155078</v>
+        <v>51.03619153657269</v>
       </c>
       <c r="F79">
-        <v>183.9733296219956</v>
+        <v>186.3625936430605</v>
       </c>
       <c r="G79">
         <v>7.11</v>
@@ -7884,28 +7884,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M79">
-        <v>13.94517838534727</v>
+        <v>14.12628459814399</v>
       </c>
       <c r="N79">
-        <v>15.4294882813194</v>
+        <v>15.24838206852268</v>
       </c>
       <c r="O79">
-        <v>3.703077187516655</v>
+        <v>3.659611696445442</v>
       </c>
       <c r="P79">
-        <v>11.72641109380274</v>
+        <v>11.58877037207724</v>
       </c>
       <c r="Q79">
-        <v>14.52641109380274</v>
+        <v>14.38877037207724</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.7387326218559117</v>
+        <v>0.7680967930916649</v>
       </c>
       <c r="T79">
-        <v>3.404635870424966</v>
+        <v>3.548912972615336</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7922,7 +7922,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.106438932149605</v>
+        <v>2.079433304814354</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7930,22 +7930,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2139155344801663</v>
+        <v>0.2135644059334729</v>
       </c>
       <c r="C80">
-        <v>121.2824655337094</v>
+        <v>119.5222171728615</v>
       </c>
       <c r="D80">
-        <v>300.5350591767699</v>
+        <v>301.1640748369869</v>
       </c>
       <c r="E80">
-        <v>51.03619153657269</v>
+        <v>53.42545555763755</v>
       </c>
       <c r="F80">
-        <v>186.3625936430605</v>
+        <v>188.7518576641254</v>
       </c>
       <c r="G80">
         <v>7.11</v>
@@ -7966,28 +7966,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M80">
-        <v>14.12628459814399</v>
+        <v>14.30739081094071</v>
       </c>
       <c r="N80">
-        <v>15.24838206852268</v>
+        <v>15.06727585572596</v>
       </c>
       <c r="O80">
-        <v>3.659611696445442</v>
+        <v>3.61614620537423</v>
       </c>
       <c r="P80">
-        <v>11.58877037207724</v>
+        <v>11.45112965035173</v>
       </c>
       <c r="Q80">
-        <v>14.38877037207724</v>
+        <v>14.25112965035173</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.7680967930916649</v>
+        <v>0.8002575520641567</v>
       </c>
       <c r="T80">
-        <v>3.548912972615336</v>
+        <v>3.70693075120479</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.079433304814354</v>
+        <v>2.053111364247084</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8012,22 +8012,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2135644059334729</v>
+        <v>0.2132132773867795</v>
       </c>
       <c r="C81">
-        <v>119.5222171728615</v>
+        <v>117.7646073763864</v>
       </c>
       <c r="D81">
-        <v>301.1640748369869</v>
+        <v>301.7957290615767</v>
       </c>
       <c r="E81">
-        <v>53.42545555763755</v>
+        <v>55.81471957870244</v>
       </c>
       <c r="F81">
-        <v>188.7518576641254</v>
+        <v>191.1411216851903</v>
       </c>
       <c r="G81">
         <v>7.11</v>
@@ -8048,28 +8048,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M81">
-        <v>14.30739081094071</v>
+        <v>14.48849702373743</v>
       </c>
       <c r="N81">
-        <v>15.06727585572596</v>
+        <v>14.88616964292924</v>
       </c>
       <c r="O81">
-        <v>3.61614620537423</v>
+        <v>3.572680714303018</v>
       </c>
       <c r="P81">
-        <v>11.45112965035173</v>
+        <v>11.31348892862622</v>
       </c>
       <c r="Q81">
-        <v>14.25112965035173</v>
+        <v>14.11348892862623</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.8002575520641567</v>
+        <v>0.8356343869338976</v>
       </c>
       <c r="T81">
-        <v>3.70693075120479</v>
+        <v>3.880750307653189</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.053111364247084</v>
+        <v>2.027447472193995</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8094,22 +8094,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2132132773867795</v>
+        <v>0.2128621488400861</v>
       </c>
       <c r="C82">
-        <v>117.7646073763864</v>
+        <v>116.009652781361</v>
       </c>
       <c r="D82">
-        <v>301.7957290615767</v>
+        <v>302.4300384876161</v>
       </c>
       <c r="E82">
-        <v>55.81471957870244</v>
+        <v>58.20398359976733</v>
       </c>
       <c r="F82">
-        <v>191.1411216851903</v>
+        <v>193.5303857062552</v>
       </c>
       <c r="G82">
         <v>7.11</v>
@@ -8130,28 +8130,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M82">
-        <v>14.48849702373743</v>
+        <v>14.66960323653414</v>
       </c>
       <c r="N82">
-        <v>14.88616964292924</v>
+        <v>14.70506343013252</v>
       </c>
       <c r="O82">
-        <v>3.572680714303018</v>
+        <v>3.529215223231805</v>
       </c>
       <c r="P82">
-        <v>11.31348892862622</v>
+        <v>11.17584820690072</v>
       </c>
       <c r="Q82">
-        <v>14.11348892862623</v>
+        <v>13.97584820690072</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.8356343869338976</v>
+        <v>0.8747350991583479</v>
       </c>
       <c r="T82">
-        <v>3.880750307653189</v>
+        <v>4.072866659517207</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8168,7 +8168,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.027447472193995</v>
+        <v>2.002417256487896</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8176,22 +8176,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2128621488400861</v>
+        <v>0.2213604602933927</v>
       </c>
       <c r="C83">
-        <v>116.009652781361</v>
+        <v>98.9807332501197</v>
       </c>
       <c r="D83">
-        <v>302.4300384876161</v>
+        <v>287.7903829774397</v>
       </c>
       <c r="E83">
-        <v>58.20398359976733</v>
+        <v>60.59324762083219</v>
       </c>
       <c r="F83">
-        <v>193.5303857062552</v>
+        <v>195.91964972732</v>
       </c>
       <c r="G83">
         <v>7.11</v>
@@ -8212,45 +8212,45 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M83">
-        <v>14.66960323653414</v>
+        <v>17.6327684754588</v>
       </c>
       <c r="N83">
-        <v>14.70506343013252</v>
+        <v>11.74189819120786</v>
       </c>
       <c r="O83">
-        <v>3.529215223231805</v>
+        <v>2.818055565889887</v>
       </c>
       <c r="P83">
-        <v>11.17584820690072</v>
+        <v>8.923842625317976</v>
       </c>
       <c r="Q83">
-        <v>13.97584820690072</v>
+        <v>11.72384262531798</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.8747350991583479</v>
+        <v>0.9181803349632929</v>
       </c>
       <c r="T83">
-        <v>4.072866659517207</v>
+        <v>4.286329272699452</v>
       </c>
       <c r="U83">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V83">
         <v>0.24</v>
       </c>
       <c r="W83">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y83">
-        <v>2.002417256487896</v>
+        <v>1.66591347850737</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8258,22 +8258,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2213604602933927</v>
+        <v>0.2211172517466993</v>
       </c>
       <c r="C84">
-        <v>98.9807332501197</v>
+        <v>96.99070592766228</v>
       </c>
       <c r="D84">
-        <v>287.7903829774397</v>
+        <v>288.1896196760472</v>
       </c>
       <c r="E84">
-        <v>60.59324762083219</v>
+        <v>62.98251164189708</v>
       </c>
       <c r="F84">
-        <v>195.91964972732</v>
+        <v>198.3089137483849</v>
       </c>
       <c r="G84">
         <v>7.11</v>
@@ -8294,28 +8294,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M84">
-        <v>17.6327684754588</v>
+        <v>17.84780223735464</v>
       </c>
       <c r="N84">
-        <v>11.74189819120786</v>
+        <v>11.52686442931202</v>
       </c>
       <c r="O84">
-        <v>2.818055565889887</v>
+        <v>2.766447463034885</v>
       </c>
       <c r="P84">
-        <v>8.923842625317976</v>
+        <v>8.760416966277138</v>
       </c>
       <c r="Q84">
-        <v>11.72384262531798</v>
+        <v>11.56041696627714</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.9181803349632929</v>
+        <v>0.9667367749805843</v>
       </c>
       <c r="T84">
-        <v>4.286329272699452</v>
+        <v>4.524905134491371</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.66591347850737</v>
+        <v>1.645842231778365</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8340,22 +8340,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2211172517466993</v>
+        <v>0.2208740432000059</v>
       </c>
       <c r="C85">
-        <v>96.99070592766228</v>
+        <v>95.00178782477244</v>
       </c>
       <c r="D85">
-        <v>288.1896196760472</v>
+        <v>288.5899655942222</v>
       </c>
       <c r="E85">
-        <v>62.98251164189708</v>
+        <v>65.37177566296197</v>
       </c>
       <c r="F85">
-        <v>198.3089137483849</v>
+        <v>200.6981777694498</v>
       </c>
       <c r="G85">
         <v>7.11</v>
@@ -8376,28 +8376,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M85">
-        <v>17.84780223735464</v>
+        <v>18.06283599925048</v>
       </c>
       <c r="N85">
-        <v>11.52686442931202</v>
+        <v>11.31183066741619</v>
       </c>
       <c r="O85">
-        <v>2.766447463034885</v>
+        <v>2.714839360179884</v>
       </c>
       <c r="P85">
-        <v>8.760416966277138</v>
+        <v>8.596991307236301</v>
       </c>
       <c r="Q85">
-        <v>11.56041696627714</v>
+        <v>11.3969913072363</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.9667367749805843</v>
+        <v>1.021362770000037</v>
       </c>
       <c r="T85">
-        <v>4.524905134491371</v>
+        <v>4.793302979007281</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.645842231778365</v>
+        <v>1.626248871876242</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8422,22 +8422,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2208740432000059</v>
+        <v>0.2206308346533125</v>
       </c>
       <c r="C86">
-        <v>95.00178782477246</v>
+        <v>93.01398357058252</v>
       </c>
       <c r="D86">
-        <v>288.5899655942222</v>
+        <v>288.9914253610972</v>
       </c>
       <c r="E86">
-        <v>65.37177566296194</v>
+        <v>67.76103968402683</v>
       </c>
       <c r="F86">
-        <v>200.6981777694498</v>
+        <v>203.0874417905147</v>
       </c>
       <c r="G86">
         <v>7.11</v>
@@ -8458,28 +8458,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M86">
-        <v>18.06283599925048</v>
+        <v>18.27786976114632</v>
       </c>
       <c r="N86">
-        <v>11.31183066741619</v>
+        <v>11.09679690552035</v>
       </c>
       <c r="O86">
-        <v>2.714839360179884</v>
+        <v>2.663231257324883</v>
       </c>
       <c r="P86">
-        <v>8.596991307236301</v>
+        <v>8.433565648195463</v>
       </c>
       <c r="Q86">
-        <v>11.3969913072363</v>
+        <v>11.23356564819546</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>1.021362770000037</v>
+        <v>1.083272231022083</v>
       </c>
       <c r="T86">
-        <v>4.793302979007278</v>
+        <v>5.097487202791975</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8496,7 +8496,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.626248871876242</v>
+        <v>1.60711653220711</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8504,22 +8504,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2206308346533125</v>
+        <v>0.2203876261066191</v>
       </c>
       <c r="C87">
-        <v>93.01398357058252</v>
+        <v>91.0272978200189</v>
       </c>
       <c r="D87">
-        <v>288.9914253610972</v>
+        <v>289.3940036315984</v>
       </c>
       <c r="E87">
-        <v>67.76103968402683</v>
+        <v>70.15030370509169</v>
       </c>
       <c r="F87">
-        <v>203.0874417905147</v>
+        <v>205.4767058115795</v>
       </c>
       <c r="G87">
         <v>7.11</v>
@@ -8540,28 +8540,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M87">
-        <v>18.27786976114632</v>
+        <v>18.49290352304216</v>
       </c>
       <c r="N87">
-        <v>11.09679690552035</v>
+        <v>10.88176314362451</v>
       </c>
       <c r="O87">
-        <v>2.663231257324883</v>
+        <v>2.611623154469882</v>
       </c>
       <c r="P87">
-        <v>8.433565648195463</v>
+        <v>8.270139989154625</v>
       </c>
       <c r="Q87">
-        <v>11.23356564819546</v>
+        <v>11.07013998915463</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>1.083272231022083</v>
+        <v>1.154025900761565</v>
       </c>
       <c r="T87">
-        <v>5.097487202791975</v>
+        <v>5.445126315688772</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.60711653220711</v>
+        <v>1.588429130669818</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8586,22 +8586,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2203876261066191</v>
+        <v>0.2201444175599257</v>
       </c>
       <c r="C88">
-        <v>91.0272978200189</v>
+        <v>89.04173525398247</v>
       </c>
       <c r="D88">
-        <v>289.3940036315984</v>
+        <v>289.7977050866269</v>
       </c>
       <c r="E88">
-        <v>70.15030370509169</v>
+        <v>72.53956772615658</v>
       </c>
       <c r="F88">
-        <v>205.4767058115795</v>
+        <v>207.8659698326444</v>
       </c>
       <c r="G88">
         <v>7.11</v>
@@ -8622,28 +8622,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M88">
-        <v>18.49290352304216</v>
+        <v>18.707937284938</v>
       </c>
       <c r="N88">
-        <v>10.88176314362451</v>
+        <v>10.66672938172867</v>
       </c>
       <c r="O88">
-        <v>2.611623154469882</v>
+        <v>2.56001505161488</v>
       </c>
       <c r="P88">
-        <v>8.270139989154625</v>
+        <v>8.106714330113789</v>
       </c>
       <c r="Q88">
-        <v>11.07013998915463</v>
+        <v>10.90671433011379</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.154025900761565</v>
+        <v>1.235664750460967</v>
       </c>
       <c r="T88">
-        <v>5.445126315688772</v>
+        <v>5.84624836903123</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8660,7 +8660,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.588429130669818</v>
+        <v>1.570171324570165</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8668,22 +8668,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2201444175599257</v>
+        <v>0.2199012090132323</v>
       </c>
       <c r="C89">
-        <v>89.04173525398247</v>
+        <v>87.05730057952965</v>
       </c>
       <c r="D89">
-        <v>289.7977050866269</v>
+        <v>290.202534433239</v>
       </c>
       <c r="E89">
-        <v>72.53956772615658</v>
+        <v>74.92883174722147</v>
       </c>
       <c r="F89">
-        <v>207.8659698326444</v>
+        <v>210.2552338537093</v>
       </c>
       <c r="G89">
         <v>7.11</v>
@@ -8704,28 +8704,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M89">
-        <v>18.707937284938</v>
+        <v>18.92297104683384</v>
       </c>
       <c r="N89">
-        <v>10.66672938172867</v>
+        <v>10.45169561983283</v>
       </c>
       <c r="O89">
-        <v>2.56001505161488</v>
+        <v>2.508406948759879</v>
       </c>
       <c r="P89">
-        <v>8.106714330113789</v>
+        <v>7.943288671072951</v>
       </c>
       <c r="Q89">
-        <v>10.90671433011379</v>
+        <v>10.74328867107295</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.235664750460967</v>
+        <v>1.330910075110269</v>
       </c>
       <c r="T89">
-        <v>5.84624836903123</v>
+        <v>6.314224097930765</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8742,7 +8742,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.570171324570165</v>
+        <v>1.55232846860914</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8750,22 +8750,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2199012090132323</v>
+        <v>0.2196580004665388</v>
       </c>
       <c r="C90">
-        <v>87.05730057952965</v>
+        <v>85.0739985300558</v>
       </c>
       <c r="D90">
-        <v>290.202534433239</v>
+        <v>290.60849640483</v>
       </c>
       <c r="E90">
-        <v>74.92883174722147</v>
+        <v>77.31809576828633</v>
       </c>
       <c r="F90">
-        <v>210.2552338537093</v>
+        <v>212.6444978747742</v>
       </c>
       <c r="G90">
         <v>7.11</v>
@@ -8786,28 +8786,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M90">
-        <v>18.92297104683384</v>
+        <v>19.13800480872968</v>
       </c>
       <c r="N90">
-        <v>10.45169561983283</v>
+        <v>10.23666185793699</v>
       </c>
       <c r="O90">
-        <v>2.508406948759879</v>
+        <v>2.456798845904878</v>
       </c>
       <c r="P90">
-        <v>7.943288671072951</v>
+        <v>7.779863012032113</v>
       </c>
       <c r="Q90">
-        <v>10.74328867107295</v>
+        <v>10.57986301203211</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.330910075110269</v>
+        <v>1.443472731513989</v>
       </c>
       <c r="T90">
-        <v>6.314224097930765</v>
+        <v>6.867286322993849</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.55232846860914</v>
+        <v>1.534886575703419</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8832,22 +8832,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2196580004665388</v>
+        <v>0.2194147919198454</v>
       </c>
       <c r="C91">
-        <v>85.0739985300558</v>
+        <v>83.09183386547886</v>
       </c>
       <c r="D91">
-        <v>290.60849640483</v>
+        <v>291.0155957613179</v>
       </c>
       <c r="E91">
-        <v>77.31809576828633</v>
+        <v>79.70735978935122</v>
       </c>
       <c r="F91">
-        <v>212.6444978747742</v>
+        <v>215.0337618958391</v>
       </c>
       <c r="G91">
         <v>7.11</v>
@@ -8868,28 +8868,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M91">
-        <v>19.13800480872968</v>
+        <v>19.35303857062551</v>
       </c>
       <c r="N91">
-        <v>10.23666185793699</v>
+        <v>10.02162809604115</v>
       </c>
       <c r="O91">
-        <v>2.456798845904878</v>
+        <v>2.405190743049876</v>
       </c>
       <c r="P91">
-        <v>7.779863012032113</v>
+        <v>7.616437352991275</v>
       </c>
       <c r="Q91">
-        <v>10.57986301203211</v>
+        <v>10.41643735299128</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.443472731513989</v>
+        <v>1.578547919198455</v>
       </c>
       <c r="T91">
-        <v>6.867286322993849</v>
+        <v>7.530960993069554</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8906,7 +8906,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.534886575703419</v>
+        <v>1.517832280417826</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8914,22 +8914,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2194147919198454</v>
+        <v>0.219171583373152</v>
       </c>
       <c r="C92">
-        <v>83.09183386547886</v>
+        <v>81.11081137242672</v>
       </c>
       <c r="D92">
-        <v>291.0155957613179</v>
+        <v>291.4238372893307</v>
       </c>
       <c r="E92">
-        <v>79.70735978935122</v>
+        <v>82.09662381041611</v>
       </c>
       <c r="F92">
-        <v>215.0337618958391</v>
+        <v>217.423025916904</v>
       </c>
       <c r="G92">
         <v>7.11</v>
@@ -8950,28 +8950,28 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M92">
-        <v>19.35303857062551</v>
+        <v>19.56807233252135</v>
       </c>
       <c r="N92">
-        <v>10.02162809604115</v>
+        <v>9.806594334145313</v>
       </c>
       <c r="O92">
-        <v>2.405190743049876</v>
+        <v>2.353582640194875</v>
       </c>
       <c r="P92">
-        <v>7.616437352991275</v>
+        <v>7.453011693950438</v>
       </c>
       <c r="Q92">
-        <v>10.41643735299128</v>
+        <v>10.25301169395044</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.578547919198455</v>
+        <v>1.743639815257245</v>
       </c>
       <c r="T92">
-        <v>7.530960993069554</v>
+        <v>8.342118923162079</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.517832280417826</v>
+        <v>1.501152804808839</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8996,22 +8996,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.219171583373152</v>
+        <v>0.2654208728770643</v>
       </c>
       <c r="C93">
-        <v>81.11081137242672</v>
+        <v>17.351490659711</v>
       </c>
       <c r="D93">
-        <v>291.4238372893307</v>
+        <v>230.0537805976798</v>
       </c>
       <c r="E93">
-        <v>82.09662381041611</v>
+        <v>84.48588783148097</v>
       </c>
       <c r="F93">
-        <v>217.423025916904</v>
+        <v>219.8122899379688</v>
       </c>
       <c r="G93">
         <v>7.11</v>
@@ -9032,45 +9032,45 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M93">
-        <v>19.56807233252135</v>
+        <v>32.26844416289382</v>
       </c>
       <c r="N93">
-        <v>9.806594334145313</v>
+        <v>-2.893777496227155</v>
       </c>
       <c r="O93">
-        <v>2.353582640194875</v>
+        <v>-0.6945065990945173</v>
       </c>
       <c r="P93">
-        <v>7.453011693950438</v>
+        <v>-2.199270897132638</v>
       </c>
       <c r="Q93">
-        <v>10.25301169395044</v>
+        <v>0.6007291028673625</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.743639815257245</v>
+        <v>1.998394155104836</v>
       </c>
       <c r="T93">
-        <v>8.342118923162079</v>
+        <v>9.593821810621021</v>
       </c>
       <c r="U93">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.24</v>
+        <v>0.2184772207922827</v>
       </c>
       <c r="W93">
-        <v>0.0684</v>
+        <v>0.1147275439876929</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y93">
-        <v>1.501152804808839</v>
+        <v>0.910321753301178</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9078,22 +9078,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2654208728770643</v>
+        <v>0.2664308728770642</v>
       </c>
       <c r="C94">
-        <v>17.351490659711</v>
+        <v>13.9090906229394</v>
       </c>
       <c r="D94">
-        <v>230.0537805976798</v>
+        <v>229.0006445819731</v>
       </c>
       <c r="E94">
-        <v>84.48588783148097</v>
+        <v>86.87515185254586</v>
       </c>
       <c r="F94">
-        <v>219.8122899379688</v>
+        <v>222.2015539590337</v>
       </c>
       <c r="G94">
         <v>7.11</v>
@@ -9114,37 +9114,37 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M94">
-        <v>32.26844416289382</v>
+        <v>32.61918812118615</v>
       </c>
       <c r="N94">
-        <v>-2.893777496227155</v>
+        <v>-3.244521454519482</v>
       </c>
       <c r="O94">
-        <v>-0.6945065990945173</v>
+        <v>-0.7786851490846757</v>
       </c>
       <c r="P94">
-        <v>-2.199270897132638</v>
+        <v>-2.465836305434807</v>
       </c>
       <c r="Q94">
-        <v>0.6007291028673625</v>
+        <v>0.334163694565194</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.998394155104836</v>
+        <v>2.277336177262669</v>
       </c>
       <c r="T94">
-        <v>9.593821810621021</v>
+        <v>10.96436778356688</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2184772207922827</v>
+        <v>0.2161280033644087</v>
       </c>
       <c r="W94">
-        <v>0.1147275439876929</v>
+        <v>0.1150724091061048</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.910321753301178</v>
+        <v>0.9005333473517029</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9160,22 +9160,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2664308728770642</v>
+        <v>0.2674408728770643</v>
       </c>
       <c r="C95">
-        <v>13.9090906229394</v>
+        <v>10.47628870191289</v>
       </c>
       <c r="D95">
-        <v>229.0006445819731</v>
+        <v>227.9571066820115</v>
       </c>
       <c r="E95">
-        <v>86.87515185254586</v>
+        <v>89.26441587361074</v>
       </c>
       <c r="F95">
-        <v>222.2015539590337</v>
+        <v>224.5908179800986</v>
       </c>
       <c r="G95">
         <v>7.11</v>
@@ -9196,37 +9196,37 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M95">
-        <v>32.61918812118615</v>
+        <v>32.96993207947848</v>
       </c>
       <c r="N95">
-        <v>-3.244521454519482</v>
+        <v>-3.595265412811809</v>
       </c>
       <c r="O95">
-        <v>-0.7786851490846757</v>
+        <v>-0.8628636990748342</v>
       </c>
       <c r="P95">
-        <v>-2.465836305434807</v>
+        <v>-2.732401713736975</v>
       </c>
       <c r="Q95">
-        <v>0.334163694565194</v>
+        <v>0.067598286263026</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>2.277336177262669</v>
+        <v>2.649258873473116</v>
       </c>
       <c r="T95">
-        <v>10.96436778356688</v>
+        <v>12.79176241416137</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2161280033644087</v>
+        <v>0.2138287692860639</v>
       </c>
       <c r="W95">
-        <v>0.1150724091061048</v>
+        <v>0.1154099366688058</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.9005333473517029</v>
+        <v>0.8909532053585996</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9242,22 +9242,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2674408728770643</v>
+        <v>0.2684508728770643</v>
       </c>
       <c r="C96">
-        <v>10.47628870191289</v>
+        <v>7.052954278276729</v>
       </c>
       <c r="D96">
-        <v>227.9571066820115</v>
+        <v>226.9230362794402</v>
       </c>
       <c r="E96">
-        <v>89.26441587361074</v>
+        <v>91.65367989467561</v>
       </c>
       <c r="F96">
-        <v>224.5908179800986</v>
+        <v>226.9800820011635</v>
       </c>
       <c r="G96">
         <v>7.11</v>
@@ -9278,37 +9278,37 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M96">
-        <v>32.96993207947848</v>
+        <v>33.3206760377708</v>
       </c>
       <c r="N96">
-        <v>-3.595265412811809</v>
+        <v>-3.946009371104129</v>
       </c>
       <c r="O96">
-        <v>-0.8628636990748342</v>
+        <v>-0.9470422490649909</v>
       </c>
       <c r="P96">
-        <v>-2.732401713736975</v>
+        <v>-2.998967122039138</v>
       </c>
       <c r="Q96">
-        <v>0.067598286263026</v>
+        <v>-0.1989671220391371</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.649258873473116</v>
+        <v>3.16995064816774</v>
       </c>
       <c r="T96">
-        <v>12.79176241416137</v>
+        <v>15.35011489699365</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2138287692860639</v>
+        <v>0.2115779401356843</v>
       </c>
       <c r="W96">
-        <v>0.1154099366688058</v>
+        <v>0.1157403583880816</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8909532053585996</v>
+        <v>0.8815747505653513</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9324,22 +9324,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2684508728770643</v>
+        <v>0.2694608728770643</v>
       </c>
       <c r="C97">
-        <v>7.052954278276729</v>
+        <v>3.638959093043411</v>
       </c>
       <c r="D97">
-        <v>226.9230362794402</v>
+        <v>225.8983051152717</v>
       </c>
       <c r="E97">
-        <v>91.65367989467561</v>
+        <v>94.04294391574049</v>
       </c>
       <c r="F97">
-        <v>226.9800820011635</v>
+        <v>229.3693460222283</v>
       </c>
       <c r="G97">
         <v>7.11</v>
@@ -9360,37 +9360,37 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M97">
-        <v>33.3206760377708</v>
+        <v>33.67141999606312</v>
       </c>
       <c r="N97">
-        <v>-3.946009371104129</v>
+        <v>-4.296753329396456</v>
       </c>
       <c r="O97">
-        <v>-0.9470422490649909</v>
+        <v>-1.031220799055149</v>
       </c>
       <c r="P97">
-        <v>-2.998967122039138</v>
+        <v>-3.265532530341306</v>
       </c>
       <c r="Q97">
-        <v>-0.1989671220391371</v>
+        <v>-0.4655325303413056</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>3.16995064816774</v>
+        <v>3.950988310209677</v>
       </c>
       <c r="T97">
-        <v>15.35011489699365</v>
+        <v>19.18764362124207</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2115779401356843</v>
+        <v>0.2093740032592709</v>
       </c>
       <c r="W97">
-        <v>0.1157403583880816</v>
+        <v>0.116063896321539</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8815747505653513</v>
+        <v>0.8723916802469621</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9406,22 +9406,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2694608728770643</v>
+        <v>0.2704708728770643</v>
       </c>
       <c r="C98">
-        <v>3.638959093043439</v>
+        <v>0.2341771935606118</v>
       </c>
       <c r="D98">
-        <v>225.8983051152717</v>
+        <v>224.8827872368538</v>
       </c>
       <c r="E98">
-        <v>94.04294391574047</v>
+        <v>96.43220793680536</v>
       </c>
       <c r="F98">
-        <v>229.3693460222283</v>
+        <v>231.7586100432932</v>
       </c>
       <c r="G98">
         <v>7.11</v>
@@ -9442,37 +9442,37 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M98">
-        <v>33.67141999606312</v>
+        <v>34.02216395435545</v>
       </c>
       <c r="N98">
-        <v>-4.296753329396456</v>
+        <v>-4.647497287688783</v>
       </c>
       <c r="O98">
-        <v>-1.031220799055149</v>
+        <v>-1.115399349045308</v>
       </c>
       <c r="P98">
-        <v>-3.265532530341306</v>
+        <v>-3.532097938643475</v>
       </c>
       <c r="Q98">
-        <v>-0.4655325303413056</v>
+        <v>-0.7320979386434741</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.950988310209666</v>
+        <v>5.252717746946223</v>
       </c>
       <c r="T98">
-        <v>19.18764362124201</v>
+        <v>25.58352482832269</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2093740032592709</v>
+        <v>0.2072155083803093</v>
       </c>
       <c r="W98">
-        <v>0.116063896321539</v>
+        <v>0.1163807633697706</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8723916802469621</v>
+        <v>0.8633979515846223</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9488,22 +9488,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2704708728770643</v>
+        <v>0.2714808728770642</v>
       </c>
       <c r="C99">
-        <v>0.2341771935606118</v>
+        <v>-3.161515118097327</v>
       </c>
       <c r="D99">
-        <v>224.8827872368538</v>
+        <v>223.8763589462608</v>
       </c>
       <c r="E99">
-        <v>96.43220793680536</v>
+        <v>98.82147195787024</v>
       </c>
       <c r="F99">
-        <v>231.7586100432932</v>
+        <v>234.1478740643581</v>
       </c>
       <c r="G99">
         <v>7.11</v>
@@ -9524,37 +9524,37 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M99">
-        <v>34.02216395435545</v>
+        <v>34.37290791264777</v>
       </c>
       <c r="N99">
-        <v>-4.647497287688783</v>
+        <v>-4.998241245981102</v>
       </c>
       <c r="O99">
-        <v>-1.115399349045308</v>
+        <v>-1.199577899035464</v>
       </c>
       <c r="P99">
-        <v>-3.532097938643475</v>
+        <v>-3.798663346945638</v>
       </c>
       <c r="Q99">
-        <v>-0.7320979386434741</v>
+        <v>-0.9986633469456372</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>5.252717746946223</v>
+        <v>7.856176620419332</v>
       </c>
       <c r="T99">
-        <v>25.58352482832269</v>
+        <v>38.37528724248403</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2072155083803093</v>
+        <v>0.205101064417245</v>
       </c>
       <c r="W99">
-        <v>0.1163807633697706</v>
+        <v>0.1166911637435484</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8633979515846223</v>
+        <v>0.8545877684051875</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9570,22 +9570,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2714808728770642</v>
+        <v>0.2724908728770642</v>
       </c>
       <c r="C100">
-        <v>-3.161515118097327</v>
+        <v>-6.548239335357863</v>
       </c>
       <c r="D100">
-        <v>223.8763589462608</v>
+        <v>222.8788987500651</v>
       </c>
       <c r="E100">
-        <v>98.82147195787024</v>
+        <v>101.2107359789351</v>
       </c>
       <c r="F100">
-        <v>234.1478740643581</v>
+        <v>236.537138085423</v>
       </c>
       <c r="G100">
         <v>7.11</v>
@@ -9606,37 +9606,37 @@
         <v>29.37466666666667</v>
       </c>
       <c r="M100">
-        <v>34.37290791264777</v>
+        <v>34.7236518709401</v>
       </c>
       <c r="N100">
-        <v>-4.998241245981102</v>
+        <v>-5.348985204273429</v>
       </c>
       <c r="O100">
-        <v>-1.199577899035464</v>
+        <v>-1.283756449025623</v>
       </c>
       <c r="P100">
-        <v>-3.798663346945638</v>
+        <v>-4.065228755247806</v>
       </c>
       <c r="Q100">
-        <v>-0.9986633469456372</v>
+        <v>-1.265228755247805</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>7.856176620419332</v>
+        <v>15.66655324083866</v>
       </c>
       <c r="T100">
-        <v>38.37528724248403</v>
+        <v>76.75057448496806</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.205101064417245</v>
+        <v>0.2030293364938384</v>
       </c>
       <c r="W100">
-        <v>0.1166911637435484</v>
+        <v>0.1169952934027045</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9644,91 +9644,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8545877684051875</v>
+        <v>0.8459555687243269</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2724908728770642</v>
-      </c>
-      <c r="C101">
-        <v>-6.548239335357863</v>
-      </c>
-      <c r="D101">
-        <v>222.8788987500651</v>
-      </c>
-      <c r="E101">
-        <v>101.2107359789351</v>
-      </c>
-      <c r="F101">
-        <v>236.537138085423</v>
-      </c>
-      <c r="G101">
-        <v>7.11</v>
-      </c>
-      <c r="H101">
-        <v>103.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>32.17466666666667</v>
-      </c>
-      <c r="K101">
-        <v>2.800000000000001</v>
-      </c>
-      <c r="L101">
-        <v>29.37466666666667</v>
-      </c>
-      <c r="M101">
-        <v>34.7236518709401</v>
-      </c>
-      <c r="N101">
-        <v>-5.348985204273429</v>
-      </c>
-      <c r="O101">
-        <v>-1.283756449025623</v>
-      </c>
-      <c r="P101">
-        <v>-4.065228755247806</v>
-      </c>
-      <c r="Q101">
-        <v>-1.265228755247805</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>15.66655324083866</v>
-      </c>
-      <c r="T101">
-        <v>76.75057448496806</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2030293364938384</v>
-      </c>
-      <c r="W101">
-        <v>0.1169952934027045</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8459555687243269</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
